--- a/docs/sphinx_setup/_static/benchmarks_files/OV-2024.4-system-info-detailed.xlsx
+++ b/docs/sphinx_setup/_static/benchmarks_files/OV-2024.4-system-info-detailed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://intel-my.sharepoint.com/personal/michael_f_hansen_intel_com/Documents/Documents/NCS/IoTG-Benchmarking/OV_release_by_release/OV-2024.4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F33956F-2550-4697-ABB3-9F1C263C6B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2CE4605-2BF1-4EE1-84BC-AD8D479A905A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31125" yWindow="4050" windowWidth="26775" windowHeight="13770" xr2:uid="{619B73C1-0C67-4D01-B9EA-8D8654122857}"/>
+    <workbookView xWindow="-32220" yWindow="1260" windowWidth="29730" windowHeight="18450" xr2:uid="{998B3E1D-00F3-406A-8CA3-570363B076DA}"/>
   </bookViews>
   <sheets>
     <sheet name="sysinfo" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5618" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5615" uniqueCount="436">
   <si>
     <t>Intel® Processor N100</t>
   </si>
@@ -1038,9 +1038,6 @@
     <t>CPU0_DIMM_B0</t>
   </si>
   <si>
-    <t>Ubuntu 20.04.6 LTS</t>
-  </si>
-  <si>
     <t>Ubuntu 22.04.6 LTS</t>
   </si>
   <si>
@@ -1056,13 +1053,7 @@
     <t>Software</t>
   </si>
   <si>
-    <t>5.150-87-generic</t>
-  </si>
-  <si>
-    <t>5.15.47+prerelease6469.7</t>
-  </si>
-  <si>
-    <t>5.4.0-81-generic</t>
+    <t>6.5.10-060510-generic</t>
   </si>
   <si>
     <t>6.5.0-28-generic</t>
@@ -1131,7 +1122,7 @@
     <t>OpenVINO</t>
   </si>
   <si>
-    <t>2024.1</t>
+    <t>2024.4</t>
   </si>
   <si>
     <t>Ubuntu 22.04.3 LTS</t>
@@ -1152,9 +1143,6 @@
     <t>2022.3.0-8891</t>
   </si>
   <si>
-    <t>2024.1-14988</t>
-  </si>
-  <si>
     <t>6.2.0-31-generic</t>
   </si>
   <si>
@@ -1350,10 +1338,7 @@
     <t>6.2.0-41-generic</t>
   </si>
   <si>
-    <t>5.4.0-166-generic</t>
-  </si>
-  <si>
-    <t>5.4.0-163-generic</t>
+    <t>6.2.0-060200-generic</t>
   </si>
   <si>
     <t>SE5C620.86B.01.01.0007.2210270543</t>
@@ -2136,14 +2121,14 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2479,7 +2464,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{769EC8DC-FF64-4795-93D0-6B2A3FE460D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FF73C9E-B52A-45E4-9690-EBBCE7A6766D}">
   <dimension ref="A1:GI146"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
@@ -14100,7 +14085,7 @@
       </c>
       <c r="FS35" s="25"/>
       <c r="FT35" s="15" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="FV35" s="44"/>
       <c r="FW35" s="24" t="s">
@@ -14108,7 +14093,7 @@
       </c>
       <c r="FX35" s="25"/>
       <c r="FY35" s="15" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="GA35" s="44"/>
       <c r="GB35" s="24" t="s">
@@ -14116,7 +14101,7 @@
       </c>
       <c r="GC35" s="25"/>
       <c r="GD35" s="15" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="GF35" s="44"/>
       <c r="GG35" s="24" t="s">
@@ -14124,7 +14109,7 @@
       </c>
       <c r="GH35" s="25"/>
       <c r="GI35" s="15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="36" spans="1:191" ht="15" thickBot="1">
@@ -14134,7 +14119,7 @@
       </c>
       <c r="C36" s="66"/>
       <c r="D36" s="93" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E36" s="17"/>
       <c r="F36" s="89"/>
@@ -14143,7 +14128,7 @@
       </c>
       <c r="H36" s="66"/>
       <c r="I36" s="93" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J36" s="17"/>
       <c r="K36" s="41"/>
@@ -14275,7 +14260,7 @@
       </c>
       <c r="CK36" s="25"/>
       <c r="CL36" s="15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="CN36" s="100"/>
       <c r="CO36" s="24" t="s">
@@ -14283,7 +14268,7 @@
       </c>
       <c r="CP36" s="25"/>
       <c r="CQ36" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="CR36" s="101"/>
       <c r="CS36" s="89"/>
@@ -14292,7 +14277,7 @@
       </c>
       <c r="CU36" s="25"/>
       <c r="CV36" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="CW36" s="99"/>
       <c r="CX36" s="41"/>
@@ -14344,7 +14329,7 @@
         <v>220</v>
       </c>
       <c r="EB36" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="EC36" s="6"/>
       <c r="ED36" s="6"/>
@@ -14422,7 +14407,7 @@
       </c>
       <c r="FS36" s="25"/>
       <c r="FT36" s="15" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="FV36" s="54"/>
       <c r="FW36" s="24" t="s">
@@ -14430,7 +14415,7 @@
       </c>
       <c r="FX36" s="25"/>
       <c r="FY36" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="GA36" s="54"/>
       <c r="GB36" s="24" t="s">
@@ -14438,7 +14423,7 @@
       </c>
       <c r="GC36" s="25"/>
       <c r="GD36" s="15" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="GF36" s="54"/>
       <c r="GG36" s="24" t="s">
@@ -14446,19 +14431,19 @@
       </c>
       <c r="GH36" s="25"/>
       <c r="GI36" s="15" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="37" spans="1:191" ht="15" thickBot="1">
       <c r="A37" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="103"/>
       <c r="E37" s="17"/>
       <c r="F37" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G37" s="11"/>
       <c r="H37" s="11"/>
@@ -14582,20 +14567,20 @@
         <v>290</v>
       </c>
       <c r="CI37" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="CJ37" s="11"/>
       <c r="CK37" s="11"/>
       <c r="CL37" s="103"/>
       <c r="CN37" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="CO37" s="11"/>
       <c r="CP37" s="11"/>
       <c r="CQ37" s="103"/>
       <c r="CR37" s="17"/>
       <c r="CS37" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="CT37" s="11"/>
       <c r="CU37" s="11"/>
@@ -14650,10 +14635,10 @@
         <v>216</v>
       </c>
       <c r="EB37" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="EC37" s="104" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="ED37" s="105"/>
       <c r="EE37" s="106"/>
@@ -14725,25 +14710,25 @@
         <v>267</v>
       </c>
       <c r="FQ37" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="FR37" s="11"/>
       <c r="FS37" s="11"/>
       <c r="FT37" s="103"/>
       <c r="FV37" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="FW37" s="11"/>
       <c r="FX37" s="11"/>
       <c r="FY37" s="103"/>
       <c r="GA37" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="GB37" s="11"/>
       <c r="GC37" s="11"/>
       <c r="GD37" s="103"/>
       <c r="GF37" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="GG37" s="11"/>
       <c r="GH37" s="11"/>
@@ -14751,19 +14736,19 @@
     </row>
     <row r="38" spans="1:191" ht="15" thickBot="1">
       <c r="A38" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B38" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C38" s="108"/>
       <c r="D38" s="109"/>
       <c r="E38" s="17"/>
       <c r="F38" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G38" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H38" s="108"/>
       <c r="I38" s="109"/>
@@ -14792,7 +14777,7 @@
       </c>
       <c r="W38" s="66"/>
       <c r="X38" s="15" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="Y38" s="17"/>
       <c r="Z38" s="41"/>
@@ -14809,7 +14794,7 @@
       </c>
       <c r="AG38" s="25"/>
       <c r="AH38" s="15" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AJ38" s="41"/>
       <c r="AK38" s="24" t="s">
@@ -14833,7 +14818,7 @@
       </c>
       <c r="AV38" s="25"/>
       <c r="AW38" s="15" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AY38" s="41"/>
       <c r="AZ38" s="24" t="s">
@@ -14894,25 +14879,25 @@
         <v>140</v>
       </c>
       <c r="CI38" s="88" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="CJ38" s="107"/>
       <c r="CK38" s="108"/>
       <c r="CL38" s="109"/>
       <c r="CN38" s="88" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="CO38" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="CP38" s="108"/>
       <c r="CQ38" s="109"/>
       <c r="CR38" s="110"/>
       <c r="CS38" s="88" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="CT38" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="CU38" s="108"/>
       <c r="CV38" s="109"/>
@@ -14964,10 +14949,10 @@
       <c r="DY38" s="30"/>
       <c r="DZ38" s="85"/>
       <c r="EB38" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="EC38" s="105" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="ED38" s="105"/>
       <c r="EE38" s="106"/>
@@ -14991,7 +14976,7 @@
         <v>260</v>
       </c>
       <c r="EQ38" s="15" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="ER38" s="27"/>
       <c r="ES38" s="41"/>
@@ -14999,7 +14984,7 @@
         <v>260</v>
       </c>
       <c r="EU38" s="15" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="EV38" s="27"/>
       <c r="EW38" s="41"/>
@@ -15007,7 +14992,7 @@
         <v>260</v>
       </c>
       <c r="EY38" s="15" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="EZ38" s="27"/>
       <c r="FA38" s="55"/>
@@ -15022,69 +15007,69 @@
         <v>260</v>
       </c>
       <c r="FG38" s="15" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="FI38" s="41"/>
       <c r="FJ38" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FK38" s="15" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="FM38" s="41"/>
       <c r="FN38" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FO38" s="15" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="FQ38" s="88" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="FR38" s="107" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="FS38" s="108"/>
       <c r="FT38" s="109"/>
       <c r="FV38" s="88" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="FW38" s="107" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="FX38" s="108"/>
       <c r="FY38" s="109"/>
       <c r="GA38" s="88" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="GB38" s="107" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="GC38" s="108"/>
       <c r="GD38" s="109"/>
       <c r="GF38" s="88" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="GG38" s="107" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="GH38" s="108"/>
       <c r="GI38" s="109"/>
     </row>
     <row r="39" spans="1:191" ht="15" thickBot="1">
       <c r="A39" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B39" s="105" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D39" s="106"/>
       <c r="E39" s="17"/>
       <c r="F39" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G39" s="105" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I39" s="106"/>
       <c r="J39" s="17"/>
@@ -15193,7 +15178,7 @@
       </c>
       <c r="BP39" s="66"/>
       <c r="BQ39" s="15" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="BS39" s="64" t="s">
         <v>303</v>
@@ -15226,25 +15211,25 @@
         <v>311</v>
       </c>
       <c r="CI39" s="88" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="CJ39" s="107"/>
       <c r="CK39" s="108"/>
       <c r="CL39" s="109"/>
       <c r="CN39" s="88" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="CO39" s="107" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="CP39" s="108"/>
       <c r="CQ39" s="109"/>
       <c r="CR39" s="101"/>
       <c r="CS39" s="88" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="CT39" s="107" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="CU39" s="108"/>
       <c r="CV39" s="109"/>
@@ -15298,7 +15283,7 @@
         <v>246</v>
       </c>
       <c r="EB39" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="EC39" s="107">
         <v>2022.3</v>
@@ -15373,41 +15358,41 @@
         <v>3</v>
       </c>
       <c r="FQ39" s="88" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="FR39" s="107" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="FS39" s="108"/>
       <c r="FT39" s="109"/>
       <c r="FV39" s="88" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="FW39" s="107" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="FX39" s="108"/>
       <c r="FY39" s="109"/>
       <c r="GA39" s="88" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="GB39" s="107" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="GC39" s="108"/>
       <c r="GD39" s="109"/>
       <c r="GF39" s="88" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="GG39" s="107" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="GH39" s="108"/>
       <c r="GI39" s="109"/>
     </row>
     <row r="40" spans="1:191" ht="15" thickBot="1">
       <c r="A40" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B40" s="114" t="str">
         <f>"2024.4"</f>
@@ -15417,7 +15402,7 @@
       <c r="D40" s="116"/>
       <c r="E40" s="17"/>
       <c r="F40" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G40" s="114" t="str">
         <f>"2024.4"</f>
@@ -15432,7 +15417,7 @@
       </c>
       <c r="M40" s="112"/>
       <c r="N40" s="117" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="O40" s="17"/>
       <c r="P40" s="41"/>
@@ -15441,7 +15426,7 @@
       </c>
       <c r="R40" s="112"/>
       <c r="S40" s="117" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="T40" s="17"/>
       <c r="U40" s="41"/>
@@ -15507,7 +15492,7 @@
       </c>
       <c r="BF40" s="25"/>
       <c r="BG40" s="118" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="BI40" s="34"/>
       <c r="BJ40" s="24" t="s">
@@ -15515,7 +15500,7 @@
       </c>
       <c r="BK40" s="25"/>
       <c r="BL40" s="118" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="BN40" s="59"/>
       <c r="BO40" s="65" t="s">
@@ -15531,7 +15516,7 @@
       </c>
       <c r="BU40" s="66"/>
       <c r="BV40" s="15" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="BX40" s="34"/>
       <c r="BY40" s="24" t="s">
@@ -15539,7 +15524,7 @@
       </c>
       <c r="BZ40" s="25"/>
       <c r="CA40" s="118" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="CC40" s="34"/>
       <c r="CD40" s="24" t="s">
@@ -15547,10 +15532,10 @@
       </c>
       <c r="CE40" s="25"/>
       <c r="CF40" s="118" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="CI40" s="88" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="CJ40" s="114" t="str">
         <f>"2024.4"</f>
@@ -15559,7 +15544,7 @@
       <c r="CK40" s="115"/>
       <c r="CL40" s="116"/>
       <c r="CN40" s="88" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="CO40" s="114" t="str">
         <f>"2024.4"</f>
@@ -15569,7 +15554,7 @@
       <c r="CQ40" s="116"/>
       <c r="CR40" s="110"/>
       <c r="CS40" s="88" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="CT40" s="114" t="str">
         <f>"2024.4"</f>
@@ -15698,34 +15683,34 @@
         <v>213</v>
       </c>
       <c r="FQ40" s="88" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="FR40" s="114" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="FS40" s="115"/>
       <c r="FT40" s="116"/>
       <c r="FV40" s="88" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="FW40" s="114" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="FX40" s="115"/>
       <c r="FY40" s="116"/>
       <c r="GA40" s="88" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="GB40" s="114" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="GC40" s="115"/>
       <c r="GD40" s="116"/>
       <c r="GF40" s="88" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="GG40" s="114" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="GH40" s="115"/>
       <c r="GI40" s="116"/>
@@ -15840,7 +15825,7 @@
       </c>
       <c r="BP41" s="25"/>
       <c r="BQ41" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="BS41" s="59"/>
       <c r="BT41" s="65" t="s">
@@ -15867,27 +15852,27 @@
         <v>47217</v>
       </c>
       <c r="CI41" s="88" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="CJ41" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="CK41" s="108"/>
       <c r="CL41" s="109"/>
       <c r="CN41" s="88" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="CO41" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="CP41" s="108"/>
       <c r="CQ41" s="109"/>
       <c r="CR41" s="110"/>
       <c r="CS41" s="88" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="CT41" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="CU41" s="108"/>
       <c r="CV41" s="109"/>
@@ -15938,13 +15923,13 @@
       </c>
       <c r="DY41" s="30"/>
       <c r="DZ41" s="21" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="EB41" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="EC41" s="104" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="ED41" s="120"/>
       <c r="EE41" s="121"/>
@@ -16016,52 +16001,52 @@
         <v>216</v>
       </c>
       <c r="FQ41" s="88" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="FR41" s="107" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="FS41" s="108"/>
       <c r="FT41" s="109"/>
       <c r="FV41" s="88" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="FW41" s="107" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="FX41" s="108"/>
       <c r="FY41" s="109"/>
       <c r="GA41" s="88" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="GB41" s="107" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="GC41" s="108"/>
       <c r="GD41" s="109"/>
       <c r="GF41" s="88" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="GG41" s="107" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="GH41" s="108"/>
       <c r="GI41" s="109"/>
     </row>
     <row r="42" spans="1:191" ht="15" thickBot="1">
       <c r="A42" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B42" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C42" s="108"/>
       <c r="D42" s="109"/>
       <c r="F42" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="G42" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H42" s="108"/>
       <c r="I42" s="109"/>
@@ -16165,7 +16150,7 @@
       </c>
       <c r="BP42" s="25"/>
       <c r="BQ42" s="15" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="BS42" s="61" t="s">
         <v>325</v>
@@ -16198,27 +16183,27 @@
         <v>328</v>
       </c>
       <c r="CI42" s="88" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="CJ42" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="CK42" s="108"/>
       <c r="CL42" s="109"/>
       <c r="CN42" s="88" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="CO42" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="CP42" s="108"/>
       <c r="CQ42" s="109"/>
       <c r="CR42" s="110"/>
       <c r="CS42" s="88" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="CT42" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="CU42" s="108"/>
       <c r="CV42" s="109"/>
@@ -16266,10 +16251,10 @@
       <c r="DW42" s="80"/>
       <c r="DX42" s="78"/>
       <c r="EB42" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="EC42" s="104" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="ED42" s="120"/>
       <c r="EE42" s="121"/>
@@ -16317,7 +16302,7 @@
         <v>260</v>
       </c>
       <c r="FC42" s="15" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="FE42" s="41"/>
       <c r="FF42" s="32" t="s">
@@ -16341,53 +16326,53 @@
         <v>234</v>
       </c>
       <c r="FQ42" s="88" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="FR42" s="107" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="FS42" s="108"/>
       <c r="FT42" s="109"/>
       <c r="FV42" s="88" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="FW42" s="107" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="FX42" s="108"/>
       <c r="FY42" s="109"/>
       <c r="GA42" s="88" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="GB42" s="107" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="GC42" s="108"/>
       <c r="GD42" s="109"/>
       <c r="GF42" s="88" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="GG42" s="107" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="GH42" s="108"/>
       <c r="GI42" s="109"/>
     </row>
     <row r="43" spans="1:191" ht="15" thickBot="1">
       <c r="A43" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B43" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C43" s="108"/>
       <c r="D43" s="109"/>
       <c r="E43" s="17"/>
       <c r="F43" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="G43" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H43" s="108"/>
       <c r="I43" s="109"/>
@@ -16398,7 +16383,7 @@
       </c>
       <c r="M43" s="66"/>
       <c r="N43" s="93" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O43" s="17"/>
       <c r="P43" s="89"/>
@@ -16407,7 +16392,7 @@
       </c>
       <c r="R43" s="66"/>
       <c r="S43" s="93" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="T43" s="17"/>
       <c r="U43" s="41"/>
@@ -16473,7 +16458,7 @@
       </c>
       <c r="BF43" s="25"/>
       <c r="BG43" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BI43" s="122"/>
       <c r="BJ43" s="24" t="s">
@@ -16481,10 +16466,10 @@
       </c>
       <c r="BK43" s="25"/>
       <c r="BL43" s="15" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BN43" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="BO43" s="6"/>
       <c r="BP43" s="6"/>
@@ -16495,7 +16480,7 @@
       </c>
       <c r="BU43" s="25"/>
       <c r="BV43" s="93" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BX43" s="51"/>
       <c r="BY43" s="24" t="s">
@@ -16503,7 +16488,7 @@
       </c>
       <c r="BZ43" s="25"/>
       <c r="CA43" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="CC43" s="51"/>
       <c r="CD43" s="24" t="s">
@@ -16511,10 +16496,10 @@
       </c>
       <c r="CE43" s="25"/>
       <c r="CF43" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="CI43" s="88" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="CJ43" s="104">
         <v>20</v>
@@ -16522,7 +16507,7 @@
       <c r="CK43" s="105"/>
       <c r="CL43" s="106"/>
       <c r="CN43" s="88" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="CO43" s="104">
         <v>14</v>
@@ -16531,7 +16516,7 @@
       <c r="CQ43" s="106"/>
       <c r="CR43" s="110"/>
       <c r="CS43" s="88" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="CT43" s="104">
         <v>24</v>
@@ -16588,10 +16573,10 @@
         <v>3</v>
       </c>
       <c r="EB43" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="EC43" s="104" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="ED43" s="105"/>
       <c r="EE43" s="106"/>
@@ -16663,41 +16648,33 @@
         <v>247</v>
       </c>
       <c r="FQ43" s="88" t="s">
-        <v>376</v>
-      </c>
-      <c r="FR43" s="104">
-        <v>1</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="FR43" s="104"/>
       <c r="FS43" s="105"/>
       <c r="FT43" s="106"/>
       <c r="FV43" s="88" t="s">
-        <v>376</v>
-      </c>
-      <c r="FW43" s="104">
-        <v>1</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="FW43" s="104"/>
       <c r="FX43" s="105"/>
       <c r="FY43" s="106"/>
       <c r="GA43" s="88" t="s">
-        <v>376</v>
-      </c>
-      <c r="GB43" s="104">
-        <v>1</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="GB43" s="104"/>
       <c r="GC43" s="105"/>
       <c r="GD43" s="106"/>
       <c r="GF43" s="88" t="s">
-        <v>376</v>
-      </c>
-      <c r="GG43" s="104">
-        <v>1</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="GG43" s="104"/>
       <c r="GH43" s="105"/>
       <c r="GI43" s="106"/>
     </row>
     <row r="44" spans="1:191" ht="15" thickBot="1">
       <c r="A44" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B44" s="104">
         <v>4</v>
@@ -16706,7 +16683,7 @@
       <c r="D44" s="106"/>
       <c r="E44" s="17"/>
       <c r="F44" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="G44" s="104">
         <v>12</v>
@@ -16715,14 +16692,14 @@
       <c r="I44" s="106"/>
       <c r="J44" s="17"/>
       <c r="K44" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L44" s="11"/>
       <c r="M44" s="11"/>
       <c r="N44" s="103"/>
       <c r="O44" s="17"/>
       <c r="P44" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q44" s="11"/>
       <c r="R44" s="11"/>
@@ -16786,64 +16763,64 @@
         <v>205</v>
       </c>
       <c r="BD44" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="BE44" s="6"/>
       <c r="BF44" s="6"/>
       <c r="BG44" s="7"/>
       <c r="BI44" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="BJ44" s="6"/>
       <c r="BK44" s="6"/>
       <c r="BL44" s="7"/>
       <c r="BN44" s="88" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="BO44" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="BP44" s="108"/>
       <c r="BQ44" s="109"/>
       <c r="BS44" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="BT44" s="6"/>
       <c r="BU44" s="6"/>
       <c r="BV44" s="7"/>
       <c r="BX44" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="BY44" s="6"/>
       <c r="BZ44" s="6"/>
       <c r="CA44" s="7"/>
       <c r="CC44" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="CD44" s="6"/>
       <c r="CE44" s="6"/>
       <c r="CF44" s="7"/>
       <c r="CI44" s="88" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="CJ44" s="104" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="CK44" s="105"/>
       <c r="CL44" s="106"/>
       <c r="CN44" s="88" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="CO44" s="104" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="CP44" s="105"/>
       <c r="CQ44" s="106"/>
       <c r="CS44" s="88" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="CT44" s="104" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="CU44" s="105"/>
       <c r="CV44" s="106"/>
@@ -16968,19 +16945,19 @@
       <c r="E45" s="17"/>
       <c r="J45" s="17"/>
       <c r="K45" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="L45" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="M45" s="108"/>
       <c r="N45" s="109"/>
       <c r="O45" s="17"/>
       <c r="P45" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="Q45" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="R45" s="108"/>
       <c r="S45" s="109"/>
@@ -17000,7 +16977,7 @@
       </c>
       <c r="AB45" s="66"/>
       <c r="AC45" s="15" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AE45" s="59"/>
       <c r="AF45" s="24" t="s">
@@ -17043,50 +17020,50 @@
         <v>205</v>
       </c>
       <c r="BD45" s="88" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="BE45" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="BF45" s="108"/>
       <c r="BG45" s="109"/>
       <c r="BI45" s="88" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="BJ45" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="BK45" s="108"/>
       <c r="BL45" s="109"/>
       <c r="BN45" s="88" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="BO45" s="107" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="BP45" s="108"/>
       <c r="BQ45" s="109"/>
       <c r="BS45" s="88" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="BT45" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="BU45" s="108"/>
       <c r="BV45" s="109"/>
       <c r="BX45" s="88" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="BY45" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="BZ45" s="108"/>
       <c r="CA45" s="109"/>
       <c r="CC45" s="88" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="CD45" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="CE45" s="108"/>
       <c r="CF45" s="109"/>
@@ -17096,7 +17073,7 @@
       </c>
       <c r="CZ45" s="66"/>
       <c r="DA45" s="15" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="DC45" s="59"/>
       <c r="DD45" s="24" t="s">
@@ -17112,7 +17089,7 @@
       </c>
       <c r="DJ45" s="66"/>
       <c r="DK45" s="15" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="DM45" s="41"/>
       <c r="DN45" s="65" t="s">
@@ -17120,7 +17097,7 @@
       </c>
       <c r="DO45" s="66"/>
       <c r="DP45" s="15" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="DR45" s="41"/>
       <c r="DS45" s="65" t="s">
@@ -17128,7 +17105,7 @@
       </c>
       <c r="DT45" s="66"/>
       <c r="DU45" s="15" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="DW45" s="80"/>
       <c r="DX45" s="29" t="s">
@@ -17158,7 +17135,7 @@
         <v>260</v>
       </c>
       <c r="EQ45" s="15" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="ER45" s="27"/>
       <c r="ES45" s="41"/>
@@ -17166,7 +17143,7 @@
         <v>260</v>
       </c>
       <c r="EU45" s="15" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="EV45" s="27"/>
       <c r="EW45" s="41"/>
@@ -17174,7 +17151,7 @@
         <v>260</v>
       </c>
       <c r="EY45" s="15" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="EZ45" s="27"/>
       <c r="FA45" s="55"/>
@@ -17189,39 +17166,39 @@
         <v>260</v>
       </c>
       <c r="FG45" s="15" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="FI45" s="41"/>
       <c r="FJ45" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FK45" s="15" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="FM45" s="41"/>
       <c r="FN45" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FO45" s="15" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="46" spans="1:191" ht="15" thickBot="1">
       <c r="E46" s="17"/>
       <c r="J46" s="17"/>
       <c r="K46" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="L46" s="105" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="N46" s="106"/>
       <c r="O46" s="17"/>
       <c r="P46" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="Q46" s="105" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="S46" s="106"/>
       <c r="T46" s="17"/>
@@ -17272,7 +17249,7 @@
       </c>
       <c r="AQ46" s="66"/>
       <c r="AR46" s="15" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AT46" s="64" t="s">
         <v>277</v>
@@ -17292,26 +17269,26 @@
       </c>
       <c r="BA46" s="66"/>
       <c r="BB46" s="15" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="BD46" s="88" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="BE46" s="107" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="BF46" s="108"/>
       <c r="BG46" s="109"/>
       <c r="BI46" s="88" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="BJ46" s="107" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="BK46" s="108"/>
       <c r="BL46" s="109"/>
       <c r="BN46" s="88" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="BO46" s="114" t="str">
         <f>"2024.4"</f>
@@ -17320,26 +17297,26 @@
       <c r="BP46" s="115"/>
       <c r="BQ46" s="116"/>
       <c r="BS46" s="88" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="BT46" s="107" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="BU46" s="108"/>
       <c r="BV46" s="109"/>
       <c r="BX46" s="88" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="BY46" s="107" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="BZ46" s="108"/>
       <c r="CA46" s="109"/>
       <c r="CC46" s="88" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="CD46" s="107" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="CE46" s="108"/>
       <c r="CF46" s="109"/>
@@ -17467,7 +17444,7 @@
       <c r="E47" s="17"/>
       <c r="J47" s="17"/>
       <c r="K47" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="L47" s="114" t="str">
         <f>"2024.4"</f>
@@ -17477,7 +17454,7 @@
       <c r="N47" s="116"/>
       <c r="O47" s="17"/>
       <c r="P47" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="Q47" s="114" t="str">
         <f>"2024.4"</f>
@@ -17492,7 +17469,7 @@
       </c>
       <c r="W47" s="66"/>
       <c r="X47" s="15" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="Y47" s="17"/>
       <c r="Z47" s="41"/>
@@ -17517,7 +17494,7 @@
       </c>
       <c r="AL47" s="66"/>
       <c r="AM47" s="15" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AO47" s="41"/>
       <c r="AP47" s="65" t="s">
@@ -17525,7 +17502,7 @@
       </c>
       <c r="AQ47" s="66"/>
       <c r="AR47" s="15" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AT47" s="41"/>
       <c r="AU47" s="65" t="s">
@@ -17533,7 +17510,7 @@
       </c>
       <c r="AV47" s="66"/>
       <c r="AW47" s="15" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AY47" s="41"/>
       <c r="AZ47" s="65" t="s">
@@ -17541,10 +17518,10 @@
       </c>
       <c r="BA47" s="66"/>
       <c r="BB47" s="15" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BD47" s="88" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="BE47" s="114" t="str">
         <f>"2024.4"</f>
@@ -17553,7 +17530,7 @@
       <c r="BF47" s="115"/>
       <c r="BG47" s="116"/>
       <c r="BI47" s="88" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="BJ47" s="114" t="str">
         <f>"2024.4"</f>
@@ -17566,7 +17543,7 @@
       <c r="BP47" s="108"/>
       <c r="BQ47" s="109"/>
       <c r="BS47" s="88" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="BT47" s="114" t="str">
         <f>"2024.4"</f>
@@ -17575,7 +17552,7 @@
       <c r="BU47" s="115"/>
       <c r="BV47" s="116"/>
       <c r="BX47" s="88" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="BY47" s="114" t="str">
         <f>"2024.4"</f>
@@ -17584,7 +17561,7 @@
       <c r="BZ47" s="115"/>
       <c r="CA47" s="116"/>
       <c r="CC47" s="88" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="CD47" s="114" t="str">
         <f>"2024.4"</f>
@@ -17598,7 +17575,7 @@
       </c>
       <c r="CZ47" s="66"/>
       <c r="DA47" s="15" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="DC47" s="41"/>
       <c r="DD47" s="65" t="s">
@@ -17606,7 +17583,7 @@
       </c>
       <c r="DE47" s="66"/>
       <c r="DF47" s="15" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="DH47" s="41"/>
       <c r="DI47" s="65" t="s">
@@ -17789,10 +17766,10 @@
       <c r="BK48" s="108"/>
       <c r="BL48" s="109"/>
       <c r="BN48" s="88" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="BO48" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="BP48" s="108"/>
       <c r="BQ48" s="109"/>
@@ -17928,19 +17905,19 @@
       <c r="E49" s="17"/>
       <c r="J49" s="17"/>
       <c r="K49" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="L49" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="M49" s="108"/>
       <c r="N49" s="109"/>
       <c r="O49" s="17"/>
       <c r="P49" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="Q49" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="R49" s="108"/>
       <c r="S49" s="109"/>
@@ -17986,7 +17963,7 @@
       </c>
       <c r="AQ49" s="66"/>
       <c r="AR49" s="15" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="AT49" s="41"/>
       <c r="AU49" s="65" t="s">
@@ -18004,53 +17981,53 @@
       </c>
       <c r="BA49" s="66"/>
       <c r="BB49" s="15" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BD49" s="88" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="BE49" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="BF49" s="108"/>
       <c r="BG49" s="109"/>
       <c r="BI49" s="88" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="BJ49" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="BK49" s="108"/>
       <c r="BL49" s="109"/>
       <c r="BN49" s="88" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="BO49" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="BP49" s="108"/>
       <c r="BQ49" s="109"/>
       <c r="BS49" s="88" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="BT49" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="BU49" s="108"/>
       <c r="BV49" s="109"/>
       <c r="BX49" s="88" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="BY49" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="BZ49" s="108"/>
       <c r="CA49" s="109"/>
       <c r="CC49" s="88" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="CD49" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="CE49" s="108"/>
       <c r="CF49" s="109"/>
@@ -18146,7 +18123,7 @@
         <v>260</v>
       </c>
       <c r="FC49" s="15" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="FE49" s="41"/>
       <c r="FF49" s="32" t="s">
@@ -18172,18 +18149,18 @@
     </row>
     <row r="50" spans="5:171" ht="15" thickBot="1">
       <c r="K50" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="L50" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="M50" s="108"/>
       <c r="N50" s="109"/>
       <c r="P50" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="Q50" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="R50" s="108"/>
       <c r="S50" s="109"/>
@@ -18225,7 +18202,7 @@
       </c>
       <c r="AQ50" s="66"/>
       <c r="AR50" s="15" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AT50" s="41"/>
       <c r="AU50" s="65" t="s">
@@ -18241,26 +18218,26 @@
       </c>
       <c r="BA50" s="66"/>
       <c r="BB50" s="15" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="BD50" s="88" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="BE50" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="BF50" s="108"/>
       <c r="BG50" s="109"/>
       <c r="BI50" s="88" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="BJ50" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="BK50" s="108"/>
       <c r="BL50" s="109"/>
       <c r="BN50" s="88" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="BO50" s="104">
         <v>4</v>
@@ -18268,26 +18245,26 @@
       <c r="BP50" s="105"/>
       <c r="BQ50" s="106"/>
       <c r="BS50" s="88" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="BT50" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="BU50" s="108"/>
       <c r="BV50" s="109"/>
       <c r="BX50" s="88" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="BY50" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="BZ50" s="108"/>
       <c r="CA50" s="109"/>
       <c r="CC50" s="88" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="CD50" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="CE50" s="108"/>
       <c r="CF50" s="109"/>
@@ -18405,7 +18382,7 @@
       <c r="E51" s="17"/>
       <c r="J51" s="17"/>
       <c r="K51" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="L51" s="104">
         <v>12</v>
@@ -18414,7 +18391,7 @@
       <c r="N51" s="106"/>
       <c r="O51" s="17"/>
       <c r="P51" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="Q51" s="104">
         <v>12</v>
@@ -18456,7 +18433,7 @@
         <v>290</v>
       </c>
       <c r="AO51" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AP51" s="6"/>
       <c r="AQ51" s="6"/>
@@ -18470,13 +18447,13 @@
         <v>290</v>
       </c>
       <c r="AY51" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AZ51" s="6"/>
       <c r="BA51" s="6"/>
       <c r="BB51" s="7"/>
       <c r="BD51" s="88" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="BE51" s="104">
         <v>4</v>
@@ -18484,7 +18461,7 @@
       <c r="BF51" s="105"/>
       <c r="BG51" s="106"/>
       <c r="BI51" s="88" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="BJ51" s="104">
         <v>4</v>
@@ -18492,15 +18469,15 @@
       <c r="BK51" s="105"/>
       <c r="BL51" s="106"/>
       <c r="BN51" s="88" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="BO51" s="104" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="BP51" s="105"/>
       <c r="BQ51" s="106"/>
       <c r="BS51" s="88" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="BT51" s="104">
         <v>4</v>
@@ -18508,7 +18485,7 @@
       <c r="BU51" s="105"/>
       <c r="BV51" s="106"/>
       <c r="BX51" s="88" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="BY51" s="104">
         <v>4</v>
@@ -18516,7 +18493,7 @@
       <c r="BZ51" s="105"/>
       <c r="CA51" s="106"/>
       <c r="CC51" s="88" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="CD51" s="104">
         <v>4</v>
@@ -18678,10 +18655,10 @@
         <v>140</v>
       </c>
       <c r="AO52" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AP52" s="104" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AQ52" s="105"/>
       <c r="AR52" s="106"/>
@@ -18694,50 +18671,50 @@
         <v>140</v>
       </c>
       <c r="AY52" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AZ52" s="104" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="BA52" s="105"/>
       <c r="BB52" s="106"/>
       <c r="BD52" s="88" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="BE52" s="124" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="BF52" s="125"/>
       <c r="BG52" s="126"/>
       <c r="BI52" s="88" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="BJ52" s="124" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="BK52" s="125"/>
       <c r="BL52" s="126"/>
       <c r="BS52" s="88" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="BT52" s="104" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="BU52" s="105"/>
       <c r="BV52" s="106"/>
       <c r="BX52" s="88" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="BY52" s="124" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="BZ52" s="125"/>
       <c r="CA52" s="126"/>
       <c r="CC52" s="88" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="CD52" s="124" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="CE52" s="125"/>
       <c r="CF52" s="126"/>
@@ -18763,7 +18740,7 @@
       </c>
       <c r="DJ52" s="66"/>
       <c r="DK52" s="15" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="DM52" s="41"/>
       <c r="DN52" s="65" t="s">
@@ -18771,7 +18748,7 @@
       </c>
       <c r="DO52" s="66"/>
       <c r="DP52" s="15" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="DR52" s="41"/>
       <c r="DS52" s="65" t="s">
@@ -18779,7 +18756,7 @@
       </c>
       <c r="DT52" s="66"/>
       <c r="DU52" s="15" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="DW52" s="80"/>
       <c r="DX52" s="29" t="s">
@@ -18794,14 +18771,14 @@
         <v>260</v>
       </c>
       <c r="EI52" s="15" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="EK52" s="41"/>
       <c r="EL52" s="32" t="s">
         <v>260</v>
       </c>
       <c r="EM52" s="15" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="EN52" s="27"/>
       <c r="EO52" s="41"/>
@@ -18809,7 +18786,7 @@
         <v>260</v>
       </c>
       <c r="EQ52" s="15" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="ER52" s="27"/>
       <c r="ES52" s="41"/>
@@ -18817,7 +18794,7 @@
         <v>260</v>
       </c>
       <c r="EU52" s="15" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="EV52" s="27"/>
       <c r="EW52" s="41"/>
@@ -18825,7 +18802,7 @@
         <v>260</v>
       </c>
       <c r="EY52" s="15" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="EZ52" s="27"/>
       <c r="FA52" s="55"/>
@@ -18840,21 +18817,21 @@
         <v>260</v>
       </c>
       <c r="FG52" s="15" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="FI52" s="41"/>
       <c r="FJ52" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FK52" s="15" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="FM52" s="41"/>
       <c r="FN52" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FO52" s="15" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="53" spans="5:171" ht="15" thickBot="1">
@@ -18870,7 +18847,7 @@
       </c>
       <c r="W53" s="66"/>
       <c r="X53" s="15" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="Y53" s="17"/>
       <c r="Z53" s="31" t="s">
@@ -18881,7 +18858,7 @@
       </c>
       <c r="AB53" s="66"/>
       <c r="AC53" s="15" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AE53" s="61" t="s">
         <v>303</v>
@@ -18891,7 +18868,7 @@
       </c>
       <c r="AG53" s="25"/>
       <c r="AH53" s="15" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AJ53" s="64" t="s">
         <v>303</v>
@@ -18901,13 +18878,13 @@
       </c>
       <c r="AL53" s="66"/>
       <c r="AM53" s="15" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AO53" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AP53" s="104" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AQ53" s="105"/>
       <c r="AR53" s="106"/>
@@ -18919,13 +18896,13 @@
       </c>
       <c r="AV53" s="66"/>
       <c r="AW53" s="15" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AY53" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AZ53" s="104" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="BA53" s="105"/>
       <c r="BB53" s="106"/>
@@ -18937,7 +18914,7 @@
       </c>
       <c r="CZ53" s="66"/>
       <c r="DA53" s="15" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="DC53" s="64" t="s">
         <v>303</v>
@@ -18947,7 +18924,7 @@
       </c>
       <c r="DE53" s="66"/>
       <c r="DF53" s="15" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="DH53" s="41"/>
       <c r="DI53" s="70" t="s">
@@ -19060,7 +19037,7 @@
       </c>
       <c r="W54" s="66"/>
       <c r="X54" s="15" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="Y54" s="17"/>
       <c r="Z54" s="41"/>
@@ -19085,10 +19062,10 @@
       </c>
       <c r="AL54" s="66"/>
       <c r="AM54" s="22" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="AO54" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AP54" s="107">
         <v>2022.3</v>
@@ -19101,10 +19078,10 @@
       </c>
       <c r="AV54" s="66"/>
       <c r="AW54" s="15" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AY54" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AZ54" s="107">
         <v>2022.3</v>
@@ -19117,7 +19094,7 @@
       </c>
       <c r="CZ54" s="66"/>
       <c r="DA54" s="127" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="DC54" s="41"/>
       <c r="DD54" s="65" t="s">
@@ -19408,7 +19385,7 @@
       </c>
       <c r="W56" s="66"/>
       <c r="X56" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="Y56" s="17"/>
       <c r="Z56" s="64" t="s">
@@ -19419,7 +19396,7 @@
       </c>
       <c r="AB56" s="66"/>
       <c r="AC56" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AE56" s="61" t="s">
         <v>325</v>
@@ -19429,7 +19406,7 @@
       </c>
       <c r="AG56" s="25"/>
       <c r="AH56" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AJ56" s="64" t="s">
         <v>325</v>
@@ -19439,13 +19416,13 @@
       </c>
       <c r="AL56" s="66"/>
       <c r="AM56" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AO56" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AP56" s="107" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AQ56" s="108"/>
       <c r="AR56" s="109"/>
@@ -19457,13 +19434,13 @@
       </c>
       <c r="AV56" s="66"/>
       <c r="AW56" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AY56" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AZ56" s="107" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="BA56" s="108"/>
       <c r="BB56" s="109"/>
@@ -19563,7 +19540,7 @@
         <v>260</v>
       </c>
       <c r="FC56" s="15" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="FE56" s="41"/>
       <c r="FF56" s="32" t="s">
@@ -19598,7 +19575,7 @@
       </c>
       <c r="W57" s="66"/>
       <c r="X57" s="15" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="Y57" s="17"/>
       <c r="Z57" s="89"/>
@@ -19607,7 +19584,7 @@
       </c>
       <c r="AB57" s="66"/>
       <c r="AC57" s="93" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AE57" s="122"/>
       <c r="AF57" s="24" t="s">
@@ -19615,7 +19592,7 @@
       </c>
       <c r="AG57" s="25"/>
       <c r="AH57" s="93" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AJ57" s="89"/>
       <c r="AK57" s="65" t="s">
@@ -19623,13 +19600,13 @@
       </c>
       <c r="AL57" s="66"/>
       <c r="AM57" s="15" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="AO57" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AP57" s="107" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AQ57" s="108"/>
       <c r="AR57" s="109"/>
@@ -19639,13 +19616,13 @@
       </c>
       <c r="AV57" s="66"/>
       <c r="AW57" s="15" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AY57" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AZ57" s="107" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="BA57" s="108"/>
       <c r="BB57" s="109"/>
@@ -19655,7 +19632,7 @@
       </c>
       <c r="CZ57" s="66"/>
       <c r="DA57" s="15" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="DC57" s="89"/>
       <c r="DD57" s="65" t="s">
@@ -19663,7 +19640,7 @@
       </c>
       <c r="DE57" s="66"/>
       <c r="DF57" s="15" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="DH57" s="41"/>
       <c r="DI57" s="65" t="s">
@@ -19690,7 +19667,7 @@
         <v>0</v>
       </c>
       <c r="DW57" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="DX57" s="11"/>
       <c r="DY57" s="11"/>
@@ -19769,32 +19746,32 @@
       <c r="O58" s="27"/>
       <c r="T58" s="27"/>
       <c r="U58" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="V58" s="6"/>
       <c r="W58" s="6"/>
       <c r="X58" s="7"/>
       <c r="Y58" s="27"/>
       <c r="Z58" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AA58" s="6"/>
       <c r="AB58" s="6"/>
       <c r="AC58" s="7"/>
       <c r="AE58" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AF58" s="6"/>
       <c r="AG58" s="6"/>
       <c r="AH58" s="7"/>
       <c r="AJ58" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AK58" s="6"/>
       <c r="AL58" s="6"/>
       <c r="AM58" s="7"/>
       <c r="AO58" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AP58" s="104">
         <v>4</v>
@@ -19802,13 +19779,13 @@
       <c r="AQ58" s="105"/>
       <c r="AR58" s="106"/>
       <c r="AT58" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AU58" s="6"/>
       <c r="AV58" s="6"/>
       <c r="AW58" s="7"/>
       <c r="AY58" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AZ58" s="104">
         <v>4</v>
@@ -19816,13 +19793,13 @@
       <c r="BA58" s="105"/>
       <c r="BB58" s="106"/>
       <c r="CX58" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="CY58" s="6"/>
       <c r="CZ58" s="6"/>
       <c r="DA58" s="7"/>
       <c r="DC58" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="DD58" s="11"/>
       <c r="DE58" s="11"/>
@@ -19852,10 +19829,10 @@
         <v>205</v>
       </c>
       <c r="DW58" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="DX58" s="104" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="DY58" s="105"/>
       <c r="DZ58" s="106"/>
@@ -19933,59 +19910,59 @@
       <c r="O59" s="27"/>
       <c r="T59" s="27"/>
       <c r="U59" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="V59" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="W59" s="108"/>
       <c r="X59" s="109"/>
       <c r="Y59" s="27"/>
       <c r="Z59" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AA59" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AB59" s="108"/>
       <c r="AC59" s="109"/>
       <c r="AE59" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AF59" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AG59" s="108"/>
       <c r="AH59" s="109"/>
       <c r="AJ59" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AK59" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AL59" s="108"/>
       <c r="AM59" s="109"/>
       <c r="AT59" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AU59" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AV59" s="108"/>
       <c r="AW59" s="109"/>
       <c r="CX59" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="CY59" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="CZ59" s="108"/>
       <c r="DA59" s="109"/>
       <c r="DC59" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="DD59" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="DE59" s="108"/>
       <c r="DF59" s="109"/>
@@ -20014,10 +19991,10 @@
         <v>205</v>
       </c>
       <c r="DW59" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="DX59" s="105" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="DY59" s="105"/>
       <c r="DZ59" s="106"/>
@@ -20041,7 +20018,7 @@
         <v>260</v>
       </c>
       <c r="EQ59" s="15" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="ER59" s="27"/>
       <c r="ES59" s="41"/>
@@ -20049,7 +20026,7 @@
         <v>260</v>
       </c>
       <c r="EU59" s="15" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="EV59" s="27"/>
       <c r="EW59" s="41"/>
@@ -20057,7 +20034,7 @@
         <v>260</v>
       </c>
       <c r="EY59" s="15" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="EZ59" s="27"/>
       <c r="FA59" s="55"/>
@@ -20072,21 +20049,21 @@
         <v>260</v>
       </c>
       <c r="FG59" s="15" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="FI59" s="41"/>
       <c r="FJ59" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FK59" s="15" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="FM59" s="41"/>
       <c r="FN59" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FO59" s="15" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="60" spans="5:171" ht="15" thickBot="1">
@@ -20095,58 +20072,58 @@
       <c r="O60" s="94"/>
       <c r="T60" s="94"/>
       <c r="U60" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="V60" s="105" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="X60" s="106"/>
       <c r="Y60" s="94"/>
       <c r="Z60" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AA60" s="105" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AB60" s="105"/>
       <c r="AC60" s="106"/>
       <c r="AE60" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AF60" s="105" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AG60" s="105"/>
       <c r="AH60" s="106"/>
       <c r="AJ60" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AK60" s="105" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AL60" s="105"/>
       <c r="AM60" s="106"/>
       <c r="AT60" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AU60" s="107" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AV60" s="108"/>
       <c r="AW60" s="109"/>
       <c r="CX60" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="CY60" s="105" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="CZ60" s="105"/>
       <c r="DA60" s="106"/>
       <c r="DC60" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="DD60" s="104" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="DE60" s="105"/>
       <c r="DF60" s="106"/>
@@ -20175,7 +20152,7 @@
         <v>6</v>
       </c>
       <c r="DW60" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="DX60" s="107">
         <v>2022.3</v>
@@ -20256,7 +20233,7 @@
       <c r="O61" s="94"/>
       <c r="T61" s="94"/>
       <c r="U61" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="V61" s="114" t="str">
         <f>"2024.4"</f>
@@ -20266,7 +20243,7 @@
       <c r="X61" s="116"/>
       <c r="Y61" s="94"/>
       <c r="Z61" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AA61" s="114" t="str">
         <f>"2024.4"</f>
@@ -20275,7 +20252,7 @@
       <c r="AB61" s="115"/>
       <c r="AC61" s="116"/>
       <c r="AE61" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AF61" s="114" t="str">
         <f>"2024.4"</f>
@@ -20284,7 +20261,7 @@
       <c r="AG61" s="115"/>
       <c r="AH61" s="116"/>
       <c r="AJ61" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AK61" s="114" t="str">
         <f>"2024.4"</f>
@@ -20293,7 +20270,7 @@
       <c r="AL61" s="115"/>
       <c r="AM61" s="116"/>
       <c r="AT61" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AU61" s="114" t="str">
         <f>"2024.4"</f>
@@ -20302,7 +20279,7 @@
       <c r="AV61" s="115"/>
       <c r="AW61" s="116"/>
       <c r="CX61" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="CY61" s="114" t="str">
         <f>"2024.4"</f>
@@ -20311,7 +20288,7 @@
       <c r="CZ61" s="115"/>
       <c r="DA61" s="116"/>
       <c r="DC61" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="DD61" s="114" t="str">
         <f>"2024.4"</f>
@@ -20474,10 +20451,10 @@
         <v>216</v>
       </c>
       <c r="DW62" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="DX62" s="104" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="DY62" s="120"/>
       <c r="DZ62" s="121"/>
@@ -20555,59 +20532,59 @@
       <c r="O63" s="94"/>
       <c r="T63" s="94"/>
       <c r="U63" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="V63" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="W63" s="108"/>
       <c r="X63" s="109"/>
       <c r="Y63" s="94"/>
       <c r="Z63" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AA63" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AB63" s="108"/>
       <c r="AC63" s="109"/>
       <c r="AE63" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AF63" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AG63" s="108"/>
       <c r="AH63" s="109"/>
       <c r="AJ63" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AK63" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AL63" s="108"/>
       <c r="AM63" s="109"/>
       <c r="AT63" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AU63" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AV63" s="108"/>
       <c r="AW63" s="109"/>
       <c r="CX63" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="CY63" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="CZ63" s="108"/>
       <c r="DA63" s="109"/>
       <c r="DC63" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="DD63" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="DE63" s="108"/>
       <c r="DF63" s="109"/>
@@ -20636,10 +20613,10 @@
         <v>235</v>
       </c>
       <c r="DW63" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="DX63" s="104" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="DY63" s="120"/>
       <c r="DZ63" s="121"/>
@@ -20687,7 +20664,7 @@
         <v>260</v>
       </c>
       <c r="FC63" s="15" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="FE63" s="41"/>
       <c r="FF63" s="32" t="s">
@@ -20717,59 +20694,59 @@
       <c r="O64" s="94"/>
       <c r="T64" s="94"/>
       <c r="U64" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="V64" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="W64" s="108"/>
       <c r="X64" s="109"/>
       <c r="Y64" s="94"/>
       <c r="Z64" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AA64" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AB64" s="108"/>
       <c r="AC64" s="109"/>
       <c r="AE64" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AF64" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AG64" s="108"/>
       <c r="AH64" s="109"/>
       <c r="AJ64" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AK64" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AL64" s="108"/>
       <c r="AM64" s="109"/>
       <c r="AT64" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AU64" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AV64" s="108"/>
       <c r="AW64" s="109"/>
       <c r="CX64" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="CY64" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="CZ64" s="108"/>
       <c r="DA64" s="109"/>
       <c r="DC64" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="DD64" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="DE64" s="108"/>
       <c r="DF64" s="109"/>
@@ -20798,10 +20775,10 @@
         <v>32768</v>
       </c>
       <c r="DW64" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="DX64" s="104" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="DY64" s="105"/>
       <c r="DZ64" s="106"/>
@@ -20879,7 +20856,7 @@
       <c r="O65" s="94"/>
       <c r="T65" s="94"/>
       <c r="U65" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="V65" s="104">
         <v>4</v>
@@ -20888,7 +20865,7 @@
       <c r="X65" s="106"/>
       <c r="Y65" s="94"/>
       <c r="Z65" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AA65" s="104">
         <v>6</v>
@@ -20896,7 +20873,7 @@
       <c r="AB65" s="105"/>
       <c r="AC65" s="106"/>
       <c r="AE65" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AF65" s="104">
         <v>6</v>
@@ -20904,7 +20881,7 @@
       <c r="AG65" s="105"/>
       <c r="AH65" s="106"/>
       <c r="AJ65" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AK65" s="104">
         <v>6</v>
@@ -20912,7 +20889,7 @@
       <c r="AL65" s="105"/>
       <c r="AM65" s="106"/>
       <c r="AT65" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AU65" s="104">
         <v>16</v>
@@ -20920,7 +20897,7 @@
       <c r="AV65" s="105"/>
       <c r="AW65" s="106"/>
       <c r="CX65" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="CY65" s="104">
         <v>4</v>
@@ -20928,7 +20905,7 @@
       <c r="CZ65" s="105"/>
       <c r="DA65" s="106"/>
       <c r="DC65" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="DD65" s="104">
         <v>10</v>
@@ -21037,7 +21014,7 @@
       </c>
       <c r="DJ66" s="66"/>
       <c r="DK66" s="15" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="DM66" s="41"/>
       <c r="DN66" s="65" t="s">
@@ -21045,7 +21022,7 @@
       </c>
       <c r="DO66" s="66"/>
       <c r="DP66" s="15" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="DR66" s="41"/>
       <c r="DS66" s="65" t="s">
@@ -21053,21 +21030,21 @@
       </c>
       <c r="DT66" s="66"/>
       <c r="DU66" s="15" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="EG66" s="41"/>
       <c r="EH66" s="32" t="s">
         <v>260</v>
       </c>
       <c r="EI66" s="15" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="EK66" s="41"/>
       <c r="EL66" s="32" t="s">
         <v>260</v>
       </c>
       <c r="EM66" s="15" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="EN66" s="27"/>
       <c r="EO66" s="41"/>
@@ -21075,7 +21052,7 @@
         <v>260</v>
       </c>
       <c r="EQ66" s="15" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="ER66" s="27"/>
       <c r="ES66" s="41"/>
@@ -21083,7 +21060,7 @@
         <v>260</v>
       </c>
       <c r="EU66" s="15" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="EV66" s="27"/>
       <c r="EW66" s="41"/>
@@ -21091,7 +21068,7 @@
         <v>260</v>
       </c>
       <c r="EY66" s="15" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="EZ66" s="27"/>
       <c r="FA66" s="55"/>
@@ -21106,21 +21083,21 @@
         <v>260</v>
       </c>
       <c r="FG66" s="15" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="FI66" s="41"/>
       <c r="FJ66" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FK66" s="15" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="FM66" s="41"/>
       <c r="FN66" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FO66" s="15" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="67" spans="5:171" ht="15" thickBot="1">
@@ -21483,7 +21460,7 @@
         <v>260</v>
       </c>
       <c r="FC70" s="15" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="FE70" s="41"/>
       <c r="FF70" s="32" t="s">
@@ -21709,7 +21686,7 @@
       </c>
       <c r="DJ73" s="66"/>
       <c r="DK73" s="15" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="DM73" s="41"/>
       <c r="DN73" s="65" t="s">
@@ -21717,7 +21694,7 @@
       </c>
       <c r="DO73" s="66"/>
       <c r="DP73" s="15" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="DR73" s="41"/>
       <c r="DS73" s="65" t="s">
@@ -21725,7 +21702,7 @@
       </c>
       <c r="DT73" s="66"/>
       <c r="DU73" s="15" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="EG73" s="41"/>
       <c r="EH73" s="32" t="s">
@@ -21747,7 +21724,7 @@
         <v>260</v>
       </c>
       <c r="EQ73" s="15" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="ER73" s="27"/>
       <c r="ES73" s="41"/>
@@ -21755,7 +21732,7 @@
         <v>260</v>
       </c>
       <c r="EU73" s="15" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="EV73" s="27"/>
       <c r="EW73" s="41"/>
@@ -21763,7 +21740,7 @@
         <v>260</v>
       </c>
       <c r="EY73" s="15" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="EZ73" s="27"/>
       <c r="FA73" s="55"/>
@@ -21778,21 +21755,21 @@
         <v>260</v>
       </c>
       <c r="FG73" s="15" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="FI73" s="41"/>
       <c r="FJ73" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FK73" s="15" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="FM73" s="41"/>
       <c r="FN73" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FO73" s="15" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="74" spans="5:171" ht="15" thickBot="1">
@@ -22149,7 +22126,7 @@
         <v>260</v>
       </c>
       <c r="FC77" s="15" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="FE77" s="41"/>
       <c r="FF77" s="32" t="s">
@@ -22366,7 +22343,7 @@
       </c>
       <c r="DJ80" s="66"/>
       <c r="DK80" s="15" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="DM80" s="41"/>
       <c r="DN80" s="65" t="s">
@@ -22374,7 +22351,7 @@
       </c>
       <c r="DO80" s="66"/>
       <c r="DP80" s="15" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="DR80" s="41"/>
       <c r="DS80" s="65" t="s">
@@ -22382,21 +22359,21 @@
       </c>
       <c r="DT80" s="66"/>
       <c r="DU80" s="15" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="EG80" s="41"/>
       <c r="EH80" s="32" t="s">
         <v>260</v>
       </c>
       <c r="EI80" s="15" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="EK80" s="41"/>
       <c r="EL80" s="32" t="s">
         <v>260</v>
       </c>
       <c r="EM80" s="15" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="EN80" s="27"/>
       <c r="EO80" s="41"/>
@@ -22404,7 +22381,7 @@
         <v>260</v>
       </c>
       <c r="EQ80" s="15" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="ER80" s="27"/>
       <c r="ES80" s="41"/>
@@ -22412,7 +22389,7 @@
         <v>260</v>
       </c>
       <c r="EU80" s="15" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="EV80" s="27"/>
       <c r="EW80" s="41"/>
@@ -22420,7 +22397,7 @@
         <v>260</v>
       </c>
       <c r="EY80" s="15" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="EZ80" s="27"/>
       <c r="FA80" s="55"/>
@@ -22435,21 +22412,21 @@
         <v>260</v>
       </c>
       <c r="FG80" s="15" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="FI80" s="41"/>
       <c r="FJ80" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FK80" s="15" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="FM80" s="41"/>
       <c r="FN80" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FO80" s="15" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="81" spans="112:171" ht="15" thickBot="1">
@@ -23055,7 +23032,7 @@
         <v>260</v>
       </c>
       <c r="EQ87" s="15" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="ER87" s="27"/>
       <c r="ES87" s="41"/>
@@ -23063,7 +23040,7 @@
         <v>260</v>
       </c>
       <c r="EU87" s="15" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="EV87" s="27"/>
       <c r="EW87" s="41"/>
@@ -23071,7 +23048,7 @@
         <v>260</v>
       </c>
       <c r="EY87" s="15" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="EZ87" s="27"/>
       <c r="FA87" s="55"/>
@@ -23086,21 +23063,21 @@
         <v>260</v>
       </c>
       <c r="FG87" s="15" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="FI87" s="41"/>
       <c r="FJ87" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FK87" s="15" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="FM87" s="41"/>
       <c r="FN87" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FO87" s="15" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="88" spans="112:171" ht="15" thickBot="1">
@@ -23668,7 +23645,7 @@
       </c>
       <c r="DJ94" s="66"/>
       <c r="DK94" s="15" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="DM94" s="41"/>
       <c r="DN94" s="65" t="s">
@@ -23676,7 +23653,7 @@
       </c>
       <c r="DO94" s="66"/>
       <c r="DP94" s="15" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="DR94" s="41"/>
       <c r="DS94" s="65" t="s">
@@ -23684,21 +23661,21 @@
       </c>
       <c r="DT94" s="66"/>
       <c r="DU94" s="15" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="EG94" s="41"/>
       <c r="EH94" s="32" t="s">
         <v>260</v>
       </c>
       <c r="EI94" s="15" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="EK94" s="41"/>
       <c r="EL94" s="32" t="s">
         <v>260</v>
       </c>
       <c r="EM94" s="15" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="EN94" s="27"/>
       <c r="EO94" s="41"/>
@@ -23706,7 +23683,7 @@
         <v>260</v>
       </c>
       <c r="EQ94" s="15" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="ER94" s="27"/>
       <c r="ES94" s="41"/>
@@ -23714,7 +23691,7 @@
         <v>260</v>
       </c>
       <c r="EU94" s="15" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="EV94" s="27"/>
       <c r="EW94" s="41"/>
@@ -23722,7 +23699,7 @@
         <v>260</v>
       </c>
       <c r="EY94" s="15" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="EZ94" s="27"/>
       <c r="FA94" s="55"/>
@@ -23737,21 +23714,21 @@
         <v>260</v>
       </c>
       <c r="FG94" s="15" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="FI94" s="41"/>
       <c r="FJ94" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FK94" s="15" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="FM94" s="41"/>
       <c r="FN94" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FO94" s="15" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="95" spans="112:171" ht="15" thickBot="1">
@@ -24102,7 +24079,7 @@
         <v>260</v>
       </c>
       <c r="FC98" s="15" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="FE98" s="41"/>
       <c r="FF98" s="32" t="s">
@@ -24319,7 +24296,7 @@
       </c>
       <c r="DJ101" s="66"/>
       <c r="DK101" s="15" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="DM101" s="41"/>
       <c r="DN101" s="65" t="s">
@@ -24327,7 +24304,7 @@
       </c>
       <c r="DO101" s="66"/>
       <c r="DP101" s="15" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="DR101" s="41"/>
       <c r="DS101" s="65" t="s">
@@ -24335,7 +24312,7 @@
       </c>
       <c r="DT101" s="66"/>
       <c r="DU101" s="15" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="EG101" s="41"/>
       <c r="EH101" s="32" t="s">
@@ -24357,7 +24334,7 @@
         <v>260</v>
       </c>
       <c r="EQ101" s="15" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="ER101" s="27"/>
       <c r="ES101" s="41"/>
@@ -24365,7 +24342,7 @@
         <v>260</v>
       </c>
       <c r="EU101" s="15" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="EV101" s="27"/>
       <c r="EW101" s="41"/>
@@ -24373,7 +24350,7 @@
         <v>260</v>
       </c>
       <c r="EY101" s="15" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="EZ101" s="27"/>
       <c r="FA101" s="55"/>
@@ -24388,21 +24365,21 @@
         <v>260</v>
       </c>
       <c r="FG101" s="15" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="FI101" s="41"/>
       <c r="FJ101" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FK101" s="15" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="FM101" s="41"/>
       <c r="FN101" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FO101" s="15" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="102" spans="112:171" ht="15" thickBot="1">
@@ -24753,7 +24730,7 @@
         <v>260</v>
       </c>
       <c r="FC105" s="15" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="FE105" s="41"/>
       <c r="FF105" s="32" t="s">
@@ -24970,7 +24947,7 @@
       </c>
       <c r="DJ108" s="66"/>
       <c r="DK108" s="15" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="DM108" s="41"/>
       <c r="DN108" s="65" t="s">
@@ -24978,7 +24955,7 @@
       </c>
       <c r="DO108" s="66"/>
       <c r="DP108" s="15" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="DR108" s="41"/>
       <c r="DS108" s="65" t="s">
@@ -24986,21 +24963,21 @@
       </c>
       <c r="DT108" s="66"/>
       <c r="DU108" s="15" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="EG108" s="41"/>
       <c r="EH108" s="32" t="s">
         <v>260</v>
       </c>
       <c r="EI108" s="15" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="EK108" s="41"/>
       <c r="EL108" s="32" t="s">
         <v>260</v>
       </c>
       <c r="EM108" s="15" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="EN108" s="27"/>
       <c r="EO108" s="41"/>
@@ -25008,7 +24985,7 @@
         <v>260</v>
       </c>
       <c r="EQ108" s="15" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="ER108" s="27"/>
       <c r="ES108" s="41"/>
@@ -25016,7 +24993,7 @@
         <v>260</v>
       </c>
       <c r="EU108" s="15" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="EV108" s="27"/>
       <c r="EW108" s="41"/>
@@ -25024,7 +25001,7 @@
         <v>260</v>
       </c>
       <c r="EY108" s="15" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="EZ108" s="27"/>
       <c r="FA108" s="55"/>
@@ -25039,21 +25016,21 @@
         <v>260</v>
       </c>
       <c r="FG108" s="15" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="FI108" s="41"/>
       <c r="FJ108" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FK108" s="15" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="FM108" s="41"/>
       <c r="FN108" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FO108" s="15" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="109" spans="112:171" ht="15" thickBot="1">
@@ -25404,7 +25381,7 @@
         <v>260</v>
       </c>
       <c r="FC112" s="15" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="FE112" s="41"/>
       <c r="FF112" s="32" t="s">
@@ -25659,7 +25636,7 @@
         <v>260</v>
       </c>
       <c r="EQ115" s="15" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="ER115" s="27"/>
       <c r="ES115" s="41"/>
@@ -25667,7 +25644,7 @@
         <v>260</v>
       </c>
       <c r="EU115" s="15" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="EV115" s="27"/>
       <c r="EW115" s="41"/>
@@ -25675,7 +25652,7 @@
         <v>260</v>
       </c>
       <c r="EY115" s="15" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="EZ115" s="27"/>
       <c r="FA115" s="55"/>
@@ -25690,21 +25667,21 @@
         <v>260</v>
       </c>
       <c r="FG115" s="15" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="FI115" s="41"/>
       <c r="FJ115" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FK115" s="15" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="FM115" s="41"/>
       <c r="FN115" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FO115" s="15" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="116" spans="112:171" ht="15" thickBot="1">
@@ -26055,7 +26032,7 @@
         <v>260</v>
       </c>
       <c r="FC119" s="15" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="FE119" s="41"/>
       <c r="FF119" s="32" t="s">
@@ -26272,7 +26249,7 @@
       </c>
       <c r="DJ122" s="66"/>
       <c r="DK122" s="15" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="DM122" s="41"/>
       <c r="DN122" s="65" t="s">
@@ -26280,7 +26257,7 @@
       </c>
       <c r="DO122" s="66"/>
       <c r="DP122" s="15" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="DR122" s="41"/>
       <c r="DS122" s="65" t="s">
@@ -26288,21 +26265,21 @@
       </c>
       <c r="DT122" s="66"/>
       <c r="DU122" s="15" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="EG122" s="41"/>
       <c r="EH122" s="32" t="s">
         <v>260</v>
       </c>
       <c r="EI122" s="15" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="EK122" s="41"/>
       <c r="EL122" s="32" t="s">
         <v>260</v>
       </c>
       <c r="EM122" s="15" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="EN122" s="27"/>
       <c r="EO122" s="41"/>
@@ -26310,7 +26287,7 @@
         <v>260</v>
       </c>
       <c r="EQ122" s="15" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="ER122" s="27"/>
       <c r="ES122" s="41"/>
@@ -26318,7 +26295,7 @@
         <v>260</v>
       </c>
       <c r="EU122" s="15" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="EV122" s="27"/>
       <c r="EW122" s="41"/>
@@ -26326,7 +26303,7 @@
         <v>260</v>
       </c>
       <c r="EY122" s="15" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="EZ122" s="27"/>
       <c r="FA122" s="55"/>
@@ -26341,21 +26318,21 @@
         <v>260</v>
       </c>
       <c r="FG122" s="15" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="FI122" s="41"/>
       <c r="FJ122" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FK122" s="15" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="FM122" s="41"/>
       <c r="FN122" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FO122" s="15" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="123" spans="112:171" ht="15" thickBot="1">
@@ -26706,7 +26683,7 @@
         <v>260</v>
       </c>
       <c r="FC126" s="15" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="FE126" s="73"/>
       <c r="FF126" s="32" t="s">
@@ -26923,7 +26900,7 @@
       </c>
       <c r="DJ129" s="66"/>
       <c r="DK129" s="15" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="DM129" s="59"/>
       <c r="DN129" s="65" t="s">
@@ -26931,7 +26908,7 @@
       </c>
       <c r="DO129" s="66"/>
       <c r="DP129" s="15" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="DR129" s="73"/>
       <c r="DS129" s="65" t="s">
@@ -26939,7 +26916,7 @@
       </c>
       <c r="DT129" s="66"/>
       <c r="DU129" s="15" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="EG129" s="73"/>
       <c r="EH129" s="32" t="s">
@@ -26961,7 +26938,7 @@
         <v>260</v>
       </c>
       <c r="EQ129" s="15" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="ER129" s="17"/>
       <c r="ES129" s="73"/>
@@ -26969,7 +26946,7 @@
         <v>260</v>
       </c>
       <c r="EU129" s="15" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="EV129" s="17"/>
       <c r="EW129" s="73"/>
@@ -26977,7 +26954,7 @@
         <v>260</v>
       </c>
       <c r="EY129" s="15" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="EZ129" s="27"/>
       <c r="FA129" s="55"/>
@@ -26992,21 +26969,21 @@
         <v>260</v>
       </c>
       <c r="FG129" s="15" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="FI129" s="73"/>
       <c r="FJ129" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FK129" s="15" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="FM129" s="73"/>
       <c r="FN129" s="32" t="s">
         <v>260</v>
       </c>
       <c r="FO129" s="15" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="130" spans="112:172" ht="15" thickBot="1">
@@ -27131,7 +27108,7 @@
       </c>
       <c r="DJ131" s="66"/>
       <c r="DK131" s="15" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="DM131" s="41"/>
       <c r="DN131" s="65" t="s">
@@ -27139,7 +27116,7 @@
       </c>
       <c r="DO131" s="66"/>
       <c r="DP131" s="15" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="DR131" s="41"/>
       <c r="DS131" s="65" t="s">
@@ -27147,21 +27124,21 @@
       </c>
       <c r="DT131" s="66"/>
       <c r="DU131" s="15" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="EG131" s="41"/>
       <c r="EH131" s="65" t="s">
         <v>293</v>
       </c>
       <c r="EI131" s="15" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="EK131" s="41"/>
       <c r="EL131" s="65" t="s">
         <v>293</v>
       </c>
       <c r="EM131" s="15" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="EN131" s="27"/>
       <c r="EO131" s="41"/>
@@ -27169,7 +27146,7 @@
         <v>293</v>
       </c>
       <c r="EQ131" s="15" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="ER131" s="27"/>
       <c r="ES131" s="41"/>
@@ -27177,7 +27154,7 @@
         <v>293</v>
       </c>
       <c r="EU131" s="15" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="EV131" s="27"/>
       <c r="EW131" s="41"/>
@@ -27185,7 +27162,7 @@
         <v>293</v>
       </c>
       <c r="EY131" s="15" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="EZ131" s="27"/>
       <c r="FA131" s="55"/>
@@ -27200,21 +27177,21 @@
         <v>293</v>
       </c>
       <c r="FG131" s="15" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="FI131" s="41"/>
       <c r="FJ131" s="65" t="s">
         <v>293</v>
       </c>
       <c r="FK131" s="15" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="FM131" s="41"/>
       <c r="FN131" s="65" t="s">
         <v>293</v>
       </c>
       <c r="FO131" s="15" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="132" spans="112:172" ht="15" thickBot="1">
@@ -27329,7 +27306,7 @@
       </c>
       <c r="DO133" s="66"/>
       <c r="DP133" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="DR133" s="64" t="s">
         <v>325</v>
@@ -27395,7 +27372,7 @@
         <v>260</v>
       </c>
       <c r="FC133" s="15" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="FE133" s="64" t="s">
         <v>325</v>
@@ -27404,7 +27381,7 @@
         <v>284</v>
       </c>
       <c r="FG133" s="15" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="FI133" s="64" t="s">
         <v>325</v>
@@ -27413,7 +27390,7 @@
         <v>284</v>
       </c>
       <c r="FK133" s="15" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="FM133" s="64" t="s">
         <v>325</v>
@@ -27422,7 +27399,7 @@
         <v>284</v>
       </c>
       <c r="FO133" s="15" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="134" spans="112:172" ht="15" thickBot="1">
@@ -27432,7 +27409,7 @@
       </c>
       <c r="DJ134" s="66"/>
       <c r="DK134" s="93" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="DM134" s="89"/>
       <c r="DN134" s="65" t="s">
@@ -27440,7 +27417,7 @@
       </c>
       <c r="DO134" s="66"/>
       <c r="DP134" s="15" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="DR134" s="89"/>
       <c r="DS134" s="65" t="s">
@@ -27448,21 +27425,21 @@
       </c>
       <c r="DT134" s="66"/>
       <c r="DU134" s="93" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="EG134" s="89"/>
       <c r="EH134" s="65" t="s">
         <v>326</v>
       </c>
       <c r="EI134" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="EK134" s="89"/>
       <c r="EL134" s="65" t="s">
         <v>326</v>
       </c>
       <c r="EM134" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="EN134" s="15"/>
       <c r="EO134" s="89"/>
@@ -27470,7 +27447,7 @@
         <v>326</v>
       </c>
       <c r="EQ134" s="15" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="ER134" s="15"/>
       <c r="ES134" s="89"/>
@@ -27478,7 +27455,7 @@
         <v>326</v>
       </c>
       <c r="EU134" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="EV134" s="15"/>
       <c r="EW134" s="89"/>
@@ -27486,7 +27463,7 @@
         <v>326</v>
       </c>
       <c r="EY134" s="15" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="EZ134" s="27"/>
       <c r="FA134" s="34" t="s">
@@ -27503,67 +27480,67 @@
         <v>326</v>
       </c>
       <c r="FG134" s="15" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="FI134" s="89"/>
       <c r="FJ134" s="65" t="s">
         <v>326</v>
       </c>
       <c r="FK134" s="15" t="s">
-        <v>437</v>
+        <v>337</v>
       </c>
       <c r="FM134" s="89"/>
       <c r="FN134" s="65" t="s">
         <v>326</v>
       </c>
       <c r="FO134" s="15" t="s">
-        <v>340</v>
+        <v>432</v>
       </c>
     </row>
     <row r="135" spans="112:172" ht="15" thickBot="1">
       <c r="DH135" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="DI135" s="6"/>
       <c r="DJ135" s="6"/>
       <c r="DK135" s="7"/>
       <c r="DM135" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="DN135" s="6"/>
       <c r="DO135" s="6"/>
       <c r="DP135" s="7"/>
       <c r="DR135" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="DS135" s="6"/>
       <c r="DT135" s="6"/>
       <c r="DU135" s="7"/>
       <c r="EG135" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="EH135" s="6"/>
       <c r="EI135" s="7"/>
       <c r="EK135" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="EL135" s="6"/>
       <c r="EM135" s="7"/>
       <c r="EN135" s="11"/>
       <c r="EO135" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="EP135" s="11"/>
       <c r="EQ135" s="103"/>
       <c r="ER135" s="11"/>
       <c r="ES135" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="ET135" s="11"/>
       <c r="EU135" s="103"/>
       <c r="EV135" s="11"/>
       <c r="EW135" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="EX135" s="11"/>
       <c r="EY135" s="103"/>
@@ -27573,74 +27550,74 @@
         <v>293</v>
       </c>
       <c r="FC135" s="60" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="FE135" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="FF135" s="6"/>
       <c r="FG135" s="7"/>
       <c r="FI135" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="FJ135" s="6"/>
       <c r="FK135" s="7"/>
       <c r="FM135" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="FN135" s="6"/>
       <c r="FO135" s="7"/>
     </row>
     <row r="136" spans="112:172" ht="15" thickBot="1">
       <c r="DH136" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="DI136" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="DJ136" s="108"/>
       <c r="DK136" s="109"/>
       <c r="DM136" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="DN136" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="DO136" s="108"/>
       <c r="DP136" s="109"/>
       <c r="DR136" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="DS136" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="DT136" s="108"/>
       <c r="DU136" s="109"/>
       <c r="EG136" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="EH136" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="EI136" s="108"/>
       <c r="EJ136" s="109"/>
       <c r="EK136" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="EL136" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="EM136" s="108"/>
       <c r="EN136" s="108"/>
       <c r="EO136" s="109"/>
       <c r="EP136" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="EQ136" s="108"/>
       <c r="ER136" s="110"/>
       <c r="ES136" s="110"/>
       <c r="ET136" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="EU136" s="108"/>
       <c r="EV136" s="110"/>
@@ -27656,91 +27633,91 @@
         <v>44861</v>
       </c>
       <c r="FE136" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="FF136" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="FG136" s="108"/>
       <c r="FH136" s="109"/>
       <c r="FI136" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="FJ136" s="107" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="FK136" s="108"/>
       <c r="FL136" s="109"/>
       <c r="FM136" s="88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="FN136" s="107" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="FO136" s="108"/>
       <c r="FP136" s="109"/>
     </row>
     <row r="137" spans="112:172" ht="15" thickBot="1">
       <c r="DH137" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="DI137" s="105" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="DJ137" s="105"/>
       <c r="DK137" s="106"/>
       <c r="DM137" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="DN137" s="104" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="DO137" s="105"/>
       <c r="DP137" s="106"/>
       <c r="DR137" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="DS137" s="104" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="DT137" s="105"/>
       <c r="DU137" s="106"/>
       <c r="EG137" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="EH137" s="104" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="EI137" s="106"/>
       <c r="EK137" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="EL137" s="104" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="EM137" s="106"/>
       <c r="EN137" s="130"/>
       <c r="EO137" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="EP137" s="104" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="EQ137" s="106"/>
       <c r="ER137" s="130"/>
       <c r="ES137" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="ET137" s="104" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="EU137" s="106"/>
       <c r="EV137" s="130"/>
       <c r="EW137" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="EX137" s="104" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="EY137" s="106"/>
       <c r="EZ137" s="110"/>
@@ -27751,33 +27728,33 @@
         <v>284</v>
       </c>
       <c r="FC137" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="FE137" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="FF137" s="104" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="FG137" s="106"/>
       <c r="FI137" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="FJ137" s="104" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="FK137" s="106"/>
       <c r="FM137" s="88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="FN137" s="104" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="FO137" s="106"/>
     </row>
     <row r="138" spans="112:172" ht="15" thickBot="1">
       <c r="DH138" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="DI138" s="114" t="str">
         <f>"2024.4"</f>
@@ -27786,7 +27763,7 @@
       <c r="DJ138" s="115"/>
       <c r="DK138" s="116"/>
       <c r="DM138" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="DN138" s="114" t="str">
         <f>"2024.4"</f>
@@ -27795,7 +27772,7 @@
       <c r="DO138" s="115"/>
       <c r="DP138" s="116"/>
       <c r="DR138" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="DS138" s="114" t="str">
         <f>"2024.4"</f>
@@ -27804,7 +27781,7 @@
       <c r="DT138" s="115"/>
       <c r="DU138" s="116"/>
       <c r="EG138" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="EH138" s="131" t="str">
         <f>"2024.4"</f>
@@ -27812,7 +27789,7 @@
       </c>
       <c r="EI138" s="109"/>
       <c r="EK138" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="EL138" s="131" t="str">
         <f>"2024.4"</f>
@@ -27821,7 +27798,7 @@
       <c r="EM138" s="109"/>
       <c r="EN138" s="130"/>
       <c r="EO138" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="EP138" s="131" t="str">
         <f>"2024.4"</f>
@@ -27830,7 +27807,7 @@
       <c r="EQ138" s="109"/>
       <c r="ER138" s="130"/>
       <c r="ES138" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="ET138" s="131" t="str">
         <f>"2024.4"</f>
@@ -27839,7 +27816,7 @@
       <c r="EU138" s="109"/>
       <c r="EV138" s="130"/>
       <c r="EW138" s="88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="EX138" s="131" t="str">
         <f>"2024.4"</f>
@@ -27852,29 +27829,32 @@
         <v>326</v>
       </c>
       <c r="FC138" s="15" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="FE138" s="88" t="s">
-        <v>355</v>
-      </c>
-      <c r="FF138" s="131" t="s">
-        <v>363</v>
-      </c>
-      <c r="FG138" s="109"/>
+        <v>352</v>
+      </c>
+      <c r="FF138" s="114" t="str">
+        <f>"2024.4"</f>
+        <v>2024.4</v>
+      </c>
+      <c r="FG138" s="132"/>
       <c r="FI138" s="88" t="s">
-        <v>355</v>
-      </c>
-      <c r="FJ138" s="131" t="s">
-        <v>363</v>
-      </c>
-      <c r="FK138" s="109"/>
+        <v>352</v>
+      </c>
+      <c r="FJ138" s="114" t="str">
+        <f>"2024.4"</f>
+        <v>2024.4</v>
+      </c>
+      <c r="FK138" s="132"/>
       <c r="FM138" s="88" t="s">
-        <v>355</v>
-      </c>
-      <c r="FN138" s="131" t="s">
-        <v>363</v>
-      </c>
-      <c r="FO138" s="109"/>
+        <v>352</v>
+      </c>
+      <c r="FN138" s="114" t="str">
+        <f>"2024.4"</f>
+        <v>2024.4</v>
+      </c>
+      <c r="FO138" s="132"/>
     </row>
     <row r="139" spans="112:172" ht="15" thickBot="1">
       <c r="DH139" s="88"/>
@@ -27909,209 +27889,209 @@
       <c r="EY139" s="106"/>
       <c r="EZ139" s="105"/>
       <c r="FA139" s="102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="FB139" s="11"/>
       <c r="FC139" s="103"/>
       <c r="FE139" s="88"/>
-      <c r="FF139" s="104"/>
-      <c r="FG139" s="106"/>
+      <c r="FF139" s="107"/>
+      <c r="FG139" s="109"/>
       <c r="FI139" s="88"/>
-      <c r="FJ139" s="104"/>
-      <c r="FK139" s="106"/>
+      <c r="FJ139" s="107"/>
+      <c r="FK139" s="109"/>
       <c r="FM139" s="88"/>
-      <c r="FN139" s="104"/>
-      <c r="FO139" s="106"/>
+      <c r="FN139" s="107"/>
+      <c r="FO139" s="109"/>
     </row>
     <row r="140" spans="112:172" ht="15" thickBot="1">
       <c r="DH140" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="DI140" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="DJ140" s="108"/>
       <c r="DK140" s="109"/>
       <c r="DM140" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="DN140" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="DO140" s="108"/>
       <c r="DP140" s="109"/>
       <c r="DR140" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="DS140" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="DT140" s="108"/>
       <c r="DU140" s="109"/>
       <c r="EG140" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="EH140" s="104" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="EI140" s="106"/>
       <c r="EK140" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="EL140" s="104" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="EM140" s="106"/>
       <c r="EN140" s="130"/>
       <c r="EO140" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="EP140" s="104" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="EQ140" s="106"/>
       <c r="ER140" s="130"/>
       <c r="ES140" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="ET140" s="104" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="EU140" s="106"/>
       <c r="EV140" s="130"/>
       <c r="EW140" s="88" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="EX140" s="104" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="EY140" s="106"/>
       <c r="EZ140" s="130"/>
       <c r="FA140" s="88" t="s">
-        <v>346</v>
-      </c>
-      <c r="FB140" s="132" t="s">
-        <v>344</v>
-      </c>
-      <c r="FC140" s="133"/>
+        <v>343</v>
+      </c>
+      <c r="FB140" s="133" t="s">
+        <v>341</v>
+      </c>
+      <c r="FC140" s="134"/>
       <c r="FE140" s="88" t="s">
-        <v>368</v>
-      </c>
-      <c r="FF140" s="104" t="s">
-        <v>370</v>
-      </c>
-      <c r="FG140" s="106"/>
+        <v>365</v>
+      </c>
+      <c r="FF140" s="107" t="s">
+        <v>363</v>
+      </c>
+      <c r="FG140" s="109"/>
       <c r="FI140" s="88" t="s">
-        <v>368</v>
-      </c>
-      <c r="FJ140" s="104" t="s">
-        <v>370</v>
-      </c>
-      <c r="FK140" s="106"/>
+        <v>365</v>
+      </c>
+      <c r="FJ140" s="107" t="s">
+        <v>363</v>
+      </c>
+      <c r="FK140" s="109"/>
       <c r="FM140" s="88" t="s">
-        <v>368</v>
-      </c>
-      <c r="FN140" s="104" t="s">
-        <v>370</v>
-      </c>
-      <c r="FO140" s="106"/>
+        <v>365</v>
+      </c>
+      <c r="FN140" s="107" t="s">
+        <v>363</v>
+      </c>
+      <c r="FO140" s="109"/>
     </row>
     <row r="141" spans="112:172" ht="15" thickBot="1">
       <c r="DH141" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="DI141" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="DJ141" s="108"/>
       <c r="DK141" s="109"/>
       <c r="DM141" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="DN141" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="DO141" s="108"/>
       <c r="DP141" s="109"/>
       <c r="DR141" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="DS141" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="DT141" s="108"/>
       <c r="DU141" s="109"/>
       <c r="EG141" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="EH141" s="104" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="EI141" s="106"/>
       <c r="EK141" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="EL141" s="104" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="EM141" s="106"/>
       <c r="EN141" s="130"/>
       <c r="EO141" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="EP141" s="104" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="EQ141" s="106"/>
       <c r="ER141" s="130"/>
       <c r="ES141" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="ET141" s="104" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="EU141" s="106"/>
       <c r="EV141" s="130"/>
       <c r="EW141" s="88" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="EX141" s="104" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="EY141" s="106"/>
       <c r="EZ141" s="130"/>
       <c r="FA141" s="88" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="FB141" s="107" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="FC141" s="109"/>
       <c r="FE141" s="88" t="s">
-        <v>373</v>
-      </c>
-      <c r="FF141" s="104" t="s">
-        <v>370</v>
-      </c>
-      <c r="FG141" s="106"/>
+        <v>369</v>
+      </c>
+      <c r="FF141" s="107" t="s">
+        <v>363</v>
+      </c>
+      <c r="FG141" s="109"/>
       <c r="FI141" s="88" t="s">
-        <v>373</v>
-      </c>
-      <c r="FJ141" s="104" t="s">
-        <v>370</v>
-      </c>
-      <c r="FK141" s="106"/>
+        <v>369</v>
+      </c>
+      <c r="FJ141" s="107" t="s">
+        <v>363</v>
+      </c>
+      <c r="FK141" s="109"/>
       <c r="FM141" s="88" t="s">
-        <v>373</v>
-      </c>
-      <c r="FN141" s="104" t="s">
-        <v>370</v>
-      </c>
-      <c r="FO141" s="106"/>
+        <v>369</v>
+      </c>
+      <c r="FN141" s="107" t="s">
+        <v>363</v>
+      </c>
+      <c r="FO141" s="109"/>
     </row>
     <row r="142" spans="112:172" ht="15" thickBot="1">
       <c r="DH142" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="DI142" s="104">
         <v>88</v>
@@ -28119,7 +28099,7 @@
       <c r="DJ142" s="105"/>
       <c r="DK142" s="106"/>
       <c r="DM142" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="DN142" s="104">
         <v>64</v>
@@ -28127,7 +28107,7 @@
       <c r="DO142" s="105"/>
       <c r="DP142" s="106"/>
       <c r="DR142" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="DS142" s="104">
         <v>112</v>
@@ -28135,14 +28115,14 @@
       <c r="DT142" s="105"/>
       <c r="DU142" s="106"/>
       <c r="EG142" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="EH142" s="104">
         <v>40</v>
       </c>
       <c r="EI142" s="106"/>
       <c r="EK142" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="EL142" s="104">
         <v>80</v>
@@ -28150,7 +28130,7 @@
       <c r="EM142" s="106"/>
       <c r="EN142" s="130"/>
       <c r="EO142" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="EP142" s="104">
         <v>120</v>
@@ -28158,7 +28138,7 @@
       <c r="EQ142" s="106"/>
       <c r="ER142" s="130"/>
       <c r="ES142" s="88" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="ET142" s="104">
         <v>64</v>
@@ -28166,19 +28146,21 @@
       <c r="EU142" s="106"/>
       <c r="EV142" s="130"/>
       <c r="EW142" s="88" t="s">
-        <v>377</v>
-      </c>
-      <c r="EX142" s="104"/>
+        <v>373</v>
+      </c>
+      <c r="EX142" s="104">
+        <v>8</v>
+      </c>
       <c r="EY142" s="106"/>
       <c r="EZ142" s="130"/>
       <c r="FA142" s="88" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="FB142" s="114" t="str">
         <f>"2024.4"</f>
         <v>2024.4</v>
       </c>
-      <c r="FC142" s="134"/>
+      <c r="FC142" s="132"/>
     </row>
     <row r="143" spans="112:172" ht="15" thickBot="1">
       <c r="FA143" s="88"/>
@@ -28187,25 +28169,25 @@
     </row>
     <row r="144" spans="112:172" ht="15" thickBot="1">
       <c r="FA144" s="88" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="FB144" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="FC144" s="109"/>
     </row>
     <row r="145" spans="157:159" ht="15" thickBot="1">
       <c r="FA145" s="88" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="FB145" s="107" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="FC145" s="109"/>
     </row>
     <row r="146" spans="157:159" ht="15" thickBot="1">
       <c r="FA146" s="88" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="FB146" s="104">
         <v>8</v>
@@ -28213,23 +28195,32 @@
       <c r="FC146" s="106"/>
     </row>
   </sheetData>
-  <mergeCells count="1292">
+  <mergeCells count="1301">
+    <mergeCell ref="FB142:FC142"/>
+    <mergeCell ref="FB143:FC143"/>
     <mergeCell ref="FB144:FC144"/>
     <mergeCell ref="FB145:FC145"/>
+    <mergeCell ref="FN140:FO140"/>
     <mergeCell ref="DI141:DK141"/>
     <mergeCell ref="DN141:DP141"/>
     <mergeCell ref="DS141:DU141"/>
     <mergeCell ref="FB141:FC141"/>
-    <mergeCell ref="FB142:FC142"/>
-    <mergeCell ref="FB143:FC143"/>
+    <mergeCell ref="FF141:FG141"/>
+    <mergeCell ref="FJ141:FK141"/>
+    <mergeCell ref="FN141:FO141"/>
+    <mergeCell ref="DI140:DK140"/>
+    <mergeCell ref="DN140:DP140"/>
+    <mergeCell ref="DS140:DU140"/>
+    <mergeCell ref="FB140:FC140"/>
+    <mergeCell ref="FF140:FG140"/>
+    <mergeCell ref="FJ140:FK140"/>
     <mergeCell ref="EX138:EY138"/>
     <mergeCell ref="FF138:FG138"/>
     <mergeCell ref="FJ138:FK138"/>
     <mergeCell ref="FN138:FO138"/>
-    <mergeCell ref="DI140:DK140"/>
-    <mergeCell ref="DN140:DP140"/>
-    <mergeCell ref="DS140:DU140"/>
-    <mergeCell ref="FB140:FC140"/>
+    <mergeCell ref="FF139:FG139"/>
+    <mergeCell ref="FJ139:FK139"/>
+    <mergeCell ref="FN139:FO139"/>
     <mergeCell ref="FJ136:FL136"/>
     <mergeCell ref="FN136:FP136"/>
     <mergeCell ref="FA137:FA138"/>
@@ -29508,43 +29499,43 @@
     <mergeCell ref="Z1:AC1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="AH4" r:id="rId1" display="https://ark.intel.com/search?q=i7-8700T" xr:uid="{CF33BB57-FFE6-40DE-973F-801D5B287A11}"/>
-    <hyperlink ref="AC4" r:id="rId2" display="https://ark.intel.com/search?q=i5-8500" xr:uid="{0CAB3B38-1AAA-4321-809E-1F6CA614E0B9}"/>
-    <hyperlink ref="DA4" r:id="rId3" display="https://ark.intel.com/search?q=E-2124G" xr:uid="{225AC755-196C-4701-8243-68C869F84201}"/>
-    <hyperlink ref="DK4" r:id="rId4" xr:uid="{82A08E94-554D-4021-A9E5-4AF6725FD2CE}"/>
-    <hyperlink ref="DP4" r:id="rId5" display="https://ark.intel.com/search?q=Gold+5218T" xr:uid="{72E8FE0F-2BA3-4A28-BB28-F680300953A0}"/>
-    <hyperlink ref="DU4" r:id="rId6" xr:uid="{72172F66-A7E1-49E9-851F-9B2F871BB1C2}"/>
-    <hyperlink ref="EE4" r:id="rId7" xr:uid="{C1FFA117-71D9-4692-8B0A-35309EC5CC92}"/>
-    <hyperlink ref="AM4" r:id="rId8" display="https://ark.intel.com/search?q=i5-10500TE" xr:uid="{31170656-1BC8-4269-90D5-F7CE2D0C8FFD}"/>
-    <hyperlink ref="AW4" r:id="rId9" display="https://ark.intel.com/search?q=i9-10900TE" xr:uid="{0941885B-B845-4718-B0F8-52882077F28C}"/>
-    <hyperlink ref="DF4" r:id="rId10" display="https://ark.intel.com/search?q=W-1290P" xr:uid="{11388211-E51D-4151-91CC-23F44EAAFDA6}"/>
-    <hyperlink ref="AR4" r:id="rId11" display="https://ark.intel.com/search?q=i5-10500TE" xr:uid="{BF9AE069-4881-4513-B0C2-671A84440539}"/>
-    <hyperlink ref="X4" r:id="rId12" display="https://ark.intel.com/search?q=i3-8100" xr:uid="{B93A7B44-09FF-4F85-AFAD-65F74DC7F15F}"/>
-    <hyperlink ref="BQ4" r:id="rId13" xr:uid="{B3A4FEF8-B268-4011-A0DF-C2A4141FF8CD}"/>
-    <hyperlink ref="BL4" r:id="rId14" display="https://ark.intel.com/search?q=6305E" xr:uid="{6ACE46B4-1543-4E54-A372-92E2A512F7DC}"/>
-    <hyperlink ref="DZ4" r:id="rId15" display="https://ark.intel.com/search?q=i7-7800X" xr:uid="{20D52596-4D20-4845-B248-C6C385DDE62D}"/>
-    <hyperlink ref="EI4" r:id="rId16" xr:uid="{35B723DB-E619-4A17-A1FA-E84D01ED6E89}"/>
-    <hyperlink ref="EQ4" r:id="rId17" display="Intel® Xeon® Platinum 8490H CPU @ 1.90GHz" xr:uid="{14623BD8-1245-4984-AEEB-55560ED7EFDF}"/>
-    <hyperlink ref="CV4" r:id="rId18" xr:uid="{964BE952-F42D-4D32-AE5A-D1EF3D8C464A}"/>
-    <hyperlink ref="CQ4" r:id="rId19" xr:uid="{94216051-7F05-4F27-A350-030499119EE0}"/>
-    <hyperlink ref="EM4" r:id="rId20" xr:uid="{E0F513B1-C85A-4359-83D8-99E9AEE17F86}"/>
-    <hyperlink ref="BV4" r:id="rId21" xr:uid="{1CCFCF0D-92CA-4A0D-A5E9-538CF9295A25}"/>
-    <hyperlink ref="FT4" r:id="rId22" display="11th Gen Core™ i7-11700K" xr:uid="{274869F3-DE65-4829-86A1-0B880EDF47F6}"/>
-    <hyperlink ref="FY4" r:id="rId23" xr:uid="{8ECFE762-A137-4950-ABC4-81B9CFBE8D4F}"/>
-    <hyperlink ref="GD4" r:id="rId24" xr:uid="{D47064E7-0858-447D-A843-7A5951005972}"/>
-    <hyperlink ref="FC4" r:id="rId25" xr:uid="{964B1B4B-1BD5-4381-BD15-E17E05CDE9D9}"/>
-    <hyperlink ref="EY4" r:id="rId26" display="Intel® Xeon® Gold 6448Y CPU @ 2.10GHz" xr:uid="{61FED098-4E4D-4408-B39D-1BD5FB18B77F}"/>
-    <hyperlink ref="CA4" r:id="rId27" xr:uid="{6116B985-3F61-4AF3-B93F-B24BF46FBCBE}"/>
-    <hyperlink ref="BB4" r:id="rId28" display="https://ark.intel.com/search?q=i5-10500TE" xr:uid="{21603C4D-0D95-407A-AD32-B62C5421BA73}"/>
-    <hyperlink ref="BG4" r:id="rId29" xr:uid="{528BBF1F-7598-48A8-A8C4-EAB061959CEA}"/>
-    <hyperlink ref="CF4" r:id="rId30" xr:uid="{1E38D1AF-70B9-4389-804B-BAE2AF847034}"/>
-    <hyperlink ref="CL4" r:id="rId31" display="13th Gen Intel(R) Core(TM) i5-13600K" xr:uid="{1463982F-44B4-4A6E-A467-E5E0451EA4D0}"/>
-    <hyperlink ref="EU4" r:id="rId32" xr:uid="{889E938A-55A6-42F2-82B1-CC9BF5540527}"/>
-    <hyperlink ref="GI4" r:id="rId33" xr:uid="{C469487E-6CA6-4E34-8076-44A64201F06B}"/>
-    <hyperlink ref="D4" r:id="rId34" xr:uid="{87C15C41-1D3F-405D-AFF2-BB07BA07190E}"/>
-    <hyperlink ref="I4" r:id="rId35" xr:uid="{9B72E842-EB36-4219-8163-4DCF5A1EB34B}"/>
-    <hyperlink ref="N4" r:id="rId36" xr:uid="{DB48F9F6-19F0-4F4B-A5AF-10FE9E7C5ABB}"/>
-    <hyperlink ref="S4" r:id="rId37" xr:uid="{46006A3F-DEE7-434C-B846-C94130D67295}"/>
+    <hyperlink ref="AH4" r:id="rId1" display="https://ark.intel.com/search?q=i7-8700T" xr:uid="{2EED559D-84B3-4D08-A14C-F0273B1D1AE5}"/>
+    <hyperlink ref="AC4" r:id="rId2" display="https://ark.intel.com/search?q=i5-8500" xr:uid="{0943FD22-F12A-4EDE-872A-FCD7574DD771}"/>
+    <hyperlink ref="DA4" r:id="rId3" display="https://ark.intel.com/search?q=E-2124G" xr:uid="{169AC857-B4DC-492F-AAED-136D722DAE98}"/>
+    <hyperlink ref="DK4" r:id="rId4" xr:uid="{6B026A70-0306-4B11-888E-E012DD38B463}"/>
+    <hyperlink ref="DP4" r:id="rId5" display="https://ark.intel.com/search?q=Gold+5218T" xr:uid="{5A9D730C-D7E1-4CE4-A9C6-CFD9B8EE56AC}"/>
+    <hyperlink ref="DU4" r:id="rId6" xr:uid="{B800C4F1-DA24-4AC4-AFD6-961E8CEC4B99}"/>
+    <hyperlink ref="EE4" r:id="rId7" xr:uid="{0DC96E3D-4046-4841-B89A-CBA50AC41076}"/>
+    <hyperlink ref="AM4" r:id="rId8" display="https://ark.intel.com/search?q=i5-10500TE" xr:uid="{145826FF-6859-4936-A89F-F00B486AE1EB}"/>
+    <hyperlink ref="AW4" r:id="rId9" display="https://ark.intel.com/search?q=i9-10900TE" xr:uid="{90D4BA49-1FD4-411A-A7BF-77BAAE6A393E}"/>
+    <hyperlink ref="DF4" r:id="rId10" display="https://ark.intel.com/search?q=W-1290P" xr:uid="{3D925411-D4DB-4B9D-A63E-C5804CF5E408}"/>
+    <hyperlink ref="AR4" r:id="rId11" display="https://ark.intel.com/search?q=i5-10500TE" xr:uid="{E2361C5E-5E65-4976-BEBB-B8A8E1765F7F}"/>
+    <hyperlink ref="X4" r:id="rId12" display="https://ark.intel.com/search?q=i3-8100" xr:uid="{9AF69119-F1FA-4590-939A-D62AFA9CECA7}"/>
+    <hyperlink ref="BQ4" r:id="rId13" xr:uid="{A758A657-FC6D-42BC-AD68-124229A8E27A}"/>
+    <hyperlink ref="BL4" r:id="rId14" display="https://ark.intel.com/search?q=6305E" xr:uid="{C9A1FFDD-671F-4131-906A-D1BC7E308D5D}"/>
+    <hyperlink ref="DZ4" r:id="rId15" display="https://ark.intel.com/search?q=i7-7800X" xr:uid="{E97C2DCD-9DD2-4188-BC62-35833866B00F}"/>
+    <hyperlink ref="EI4" r:id="rId16" xr:uid="{EBD3B412-3D88-4F26-A3DA-4859EF4AC765}"/>
+    <hyperlink ref="EQ4" r:id="rId17" display="Intel® Xeon® Platinum 8490H CPU @ 1.90GHz" xr:uid="{06B72A2B-7A32-4F8D-92E9-0A7AFC29FF9E}"/>
+    <hyperlink ref="CV4" r:id="rId18" xr:uid="{B804FD2A-761C-475A-B127-4DB7C1544B09}"/>
+    <hyperlink ref="CQ4" r:id="rId19" xr:uid="{6F6D4034-0F8A-44C1-9E1D-D1DBF6848674}"/>
+    <hyperlink ref="EM4" r:id="rId20" xr:uid="{E0782FA3-F9C1-4FDD-9156-AC6E73BF8122}"/>
+    <hyperlink ref="BV4" r:id="rId21" xr:uid="{9EDF83E9-8E54-4111-996B-840847169011}"/>
+    <hyperlink ref="FT4" r:id="rId22" display="11th Gen Core™ i7-11700K" xr:uid="{D34CB10B-F9C3-4A0C-8324-77D026932D12}"/>
+    <hyperlink ref="FY4" r:id="rId23" xr:uid="{517A4F6B-C248-466A-A8FF-6B62F40444BE}"/>
+    <hyperlink ref="GD4" r:id="rId24" xr:uid="{7EB6C675-F368-4233-8A7D-871D43E57F45}"/>
+    <hyperlink ref="FC4" r:id="rId25" xr:uid="{D3D8EE15-DF32-4981-8999-2BD3495C3707}"/>
+    <hyperlink ref="EY4" r:id="rId26" display="Intel® Xeon® Gold 6448Y CPU @ 2.10GHz" xr:uid="{610588EF-E1FA-4896-B6F6-52B26FFDE670}"/>
+    <hyperlink ref="CA4" r:id="rId27" xr:uid="{AAD20556-8947-4FB4-80AF-93FB9FDCC308}"/>
+    <hyperlink ref="BB4" r:id="rId28" display="https://ark.intel.com/search?q=i5-10500TE" xr:uid="{B1EDF591-EA99-47AA-A48F-742C3436267F}"/>
+    <hyperlink ref="BG4" r:id="rId29" xr:uid="{772344BF-075A-48E3-AFDB-A300664F3A90}"/>
+    <hyperlink ref="CF4" r:id="rId30" xr:uid="{476658D8-E215-43CA-9327-AC8E02E2D55C}"/>
+    <hyperlink ref="CL4" r:id="rId31" display="13th Gen Intel(R) Core(TM) i5-13600K" xr:uid="{62A9DC86-609C-49E8-8849-86E13B84B66E}"/>
+    <hyperlink ref="EU4" r:id="rId32" xr:uid="{88D1ACED-ABEA-4024-9C2C-EAD8C1D8EF50}"/>
+    <hyperlink ref="GI4" r:id="rId33" xr:uid="{5A973173-867A-4532-ACD9-DA1441BB95F9}"/>
+    <hyperlink ref="D4" r:id="rId34" xr:uid="{A05AF28F-8CF7-4BC5-8061-3A2C906A0E20}"/>
+    <hyperlink ref="I4" r:id="rId35" xr:uid="{ADD5FAB9-A4DD-49BD-ADCD-C064FB5F358D}"/>
+    <hyperlink ref="N4" r:id="rId36" xr:uid="{FC1DBA25-40D4-4EB0-B789-9696143D6C64}"/>
+    <hyperlink ref="S4" r:id="rId37" xr:uid="{8992CB1C-981D-4FBA-8A9C-6D2A532C0C29}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" r:id="rId38"/>
